--- a/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0B(杨文成 20260509).xlsx
+++ b/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0B(杨文成 20260509).xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LinWenTao\Desktop\Outbound_station\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF3C702-70EF-4AA1-9535-86D985E0BA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92436E83-2D59-4B2F-9059-56191F30E637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="版本" sheetId="3" r:id="rId1"/>
-    <sheet name="通信协议接口格式定义" sheetId="2" r:id="rId2"/>
-    <sheet name="动作列表" sheetId="1" r:id="rId3"/>
+    <sheet name="动作列表" sheetId="1" r:id="rId2"/>
+    <sheet name="通信协议接口格式定义" sheetId="2" r:id="rId3"/>
     <sheet name="接口编码表" sheetId="4" r:id="rId4"/>
     <sheet name="状态接口" sheetId="5" r:id="rId5"/>
     <sheet name="任务接口" sheetId="7" r:id="rId6"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="603">
   <si>
     <t>版本</t>
   </si>
@@ -2226,6 +2226,14 @@
   </si>
   <si>
     <t>RCS需要查询的状态：需要持续查询工作站状态，需要持续查询子设备状态是否有变更，可以直接使用1100批量查询（包含工作站和子设备所有状态），需要持续获得工作中的任务执行状态与库位信息，然后子设备的话需要持续关注状态变更标志位和异常变更标志位，如果标志位持续置0则无事发生，如果出现置1情况，则需要具体往下查询是哪个子设备状态发生了什么改变，有没有详细的信息</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ret_code</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>处理结果</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3433,6 +3441,1205 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:R181"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="49.625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="60.75" style="20" customWidth="1"/>
+    <col min="4" max="13" width="9" style="21"/>
+    <col min="14" max="14" width="9" style="21" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+    </row>
+    <row r="2" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="F2" s="84" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="86"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F3" s="87"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="89"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F4" s="90"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="91"/>
+      <c r="N4" s="91"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="91"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="92"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+    </row>
+    <row r="15" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F15" s="84" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="85"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="85"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="85"/>
+      <c r="P15" s="85"/>
+      <c r="Q15" s="85"/>
+      <c r="R15" s="86"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="F16" s="87"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="88"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="88"/>
+      <c r="K16" s="88"/>
+      <c r="L16" s="88"/>
+      <c r="M16" s="88"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="88"/>
+      <c r="P16" s="88"/>
+      <c r="Q16" s="88"/>
+      <c r="R16" s="89"/>
+    </row>
+    <row r="17" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F17" s="90"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="91"/>
+      <c r="Q17" s="91"/>
+      <c r="R17" s="92"/>
+    </row>
+    <row r="18" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
+    </row>
+    <row r="19" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+    </row>
+    <row r="21" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F21" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="81"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="81"/>
+      <c r="N21" s="81"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="81"/>
+      <c r="Q21" s="81"/>
+      <c r="R21" s="82"/>
+    </row>
+    <row r="27" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F27" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="94"/>
+      <c r="H27" s="94"/>
+      <c r="I27" s="94"/>
+      <c r="J27" s="94"/>
+      <c r="K27" s="94"/>
+      <c r="L27" s="94"/>
+      <c r="M27" s="94"/>
+      <c r="N27" s="94"/>
+      <c r="O27" s="94"/>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="94"/>
+      <c r="R27" s="95"/>
+    </row>
+    <row r="28" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F28" s="96"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="97"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="97"/>
+      <c r="N28" s="97"/>
+      <c r="O28" s="97"/>
+      <c r="P28" s="97"/>
+      <c r="Q28" s="97"/>
+      <c r="R28" s="98"/>
+    </row>
+    <row r="29" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F29" s="96"/>
+      <c r="G29" s="97"/>
+      <c r="H29" s="97"/>
+      <c r="I29" s="97"/>
+      <c r="J29" s="97"/>
+      <c r="K29" s="97"/>
+      <c r="L29" s="97"/>
+      <c r="M29" s="97"/>
+      <c r="N29" s="97"/>
+      <c r="O29" s="97"/>
+      <c r="P29" s="97"/>
+      <c r="Q29" s="97"/>
+      <c r="R29" s="98"/>
+    </row>
+    <row r="30" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F30" s="96"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="97"/>
+      <c r="J30" s="97"/>
+      <c r="K30" s="97"/>
+      <c r="L30" s="97"/>
+      <c r="M30" s="97"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="97"/>
+      <c r="P30" s="97"/>
+      <c r="Q30" s="97"/>
+      <c r="R30" s="98"/>
+    </row>
+    <row r="31" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F31" s="96"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="97"/>
+      <c r="I31" s="97"/>
+      <c r="J31" s="97"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="97"/>
+      <c r="M31" s="97"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="97"/>
+      <c r="Q31" s="97"/>
+      <c r="R31" s="98"/>
+    </row>
+    <row r="32" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F32" s="96"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="97"/>
+      <c r="I32" s="97"/>
+      <c r="J32" s="97"/>
+      <c r="K32" s="97"/>
+      <c r="L32" s="97"/>
+      <c r="M32" s="97"/>
+      <c r="N32" s="97"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="97"/>
+      <c r="Q32" s="97"/>
+      <c r="R32" s="98"/>
+    </row>
+    <row r="33" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F33" s="96"/>
+      <c r="G33" s="97"/>
+      <c r="H33" s="97"/>
+      <c r="I33" s="97"/>
+      <c r="J33" s="97"/>
+      <c r="K33" s="97"/>
+      <c r="L33" s="97"/>
+      <c r="M33" s="97"/>
+      <c r="N33" s="97"/>
+      <c r="O33" s="97"/>
+      <c r="P33" s="97"/>
+      <c r="Q33" s="97"/>
+      <c r="R33" s="98"/>
+    </row>
+    <row r="34" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F34" s="96"/>
+      <c r="G34" s="97"/>
+      <c r="H34" s="97"/>
+      <c r="I34" s="97"/>
+      <c r="J34" s="97"/>
+      <c r="K34" s="97"/>
+      <c r="L34" s="97"/>
+      <c r="M34" s="97"/>
+      <c r="N34" s="97"/>
+      <c r="O34" s="97"/>
+      <c r="P34" s="97"/>
+      <c r="Q34" s="97"/>
+      <c r="R34" s="98"/>
+    </row>
+    <row r="35" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F35" s="96"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="97"/>
+      <c r="J35" s="97"/>
+      <c r="K35" s="97"/>
+      <c r="L35" s="97"/>
+      <c r="M35" s="97"/>
+      <c r="N35" s="97"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="97"/>
+      <c r="Q35" s="97"/>
+      <c r="R35" s="98"/>
+    </row>
+    <row r="36" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F36" s="96"/>
+      <c r="G36" s="97"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="97"/>
+      <c r="J36" s="97"/>
+      <c r="K36" s="97"/>
+      <c r="L36" s="97"/>
+      <c r="M36" s="97"/>
+      <c r="N36" s="97"/>
+      <c r="O36" s="97"/>
+      <c r="P36" s="97"/>
+      <c r="Q36" s="97"/>
+      <c r="R36" s="98"/>
+    </row>
+    <row r="37" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F37" s="96"/>
+      <c r="G37" s="97"/>
+      <c r="H37" s="97"/>
+      <c r="I37" s="97"/>
+      <c r="J37" s="97"/>
+      <c r="K37" s="97"/>
+      <c r="L37" s="97"/>
+      <c r="M37" s="97"/>
+      <c r="N37" s="97"/>
+      <c r="O37" s="97"/>
+      <c r="P37" s="97"/>
+      <c r="Q37" s="97"/>
+      <c r="R37" s="98"/>
+    </row>
+    <row r="38" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F38" s="96"/>
+      <c r="G38" s="97"/>
+      <c r="H38" s="97"/>
+      <c r="I38" s="97"/>
+      <c r="J38" s="97"/>
+      <c r="K38" s="97"/>
+      <c r="L38" s="97"/>
+      <c r="M38" s="97"/>
+      <c r="N38" s="97"/>
+      <c r="O38" s="97"/>
+      <c r="P38" s="97"/>
+      <c r="Q38" s="97"/>
+      <c r="R38" s="98"/>
+    </row>
+    <row r="39" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F39" s="96"/>
+      <c r="G39" s="97"/>
+      <c r="H39" s="97"/>
+      <c r="I39" s="97"/>
+      <c r="J39" s="97"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="97"/>
+      <c r="M39" s="97"/>
+      <c r="N39" s="97"/>
+      <c r="O39" s="97"/>
+      <c r="P39" s="97"/>
+      <c r="Q39" s="97"/>
+      <c r="R39" s="98"/>
+    </row>
+    <row r="40" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F40" s="96"/>
+      <c r="G40" s="97"/>
+      <c r="H40" s="97"/>
+      <c r="I40" s="97"/>
+      <c r="J40" s="97"/>
+      <c r="K40" s="97"/>
+      <c r="L40" s="97"/>
+      <c r="M40" s="97"/>
+      <c r="N40" s="97"/>
+      <c r="O40" s="97"/>
+      <c r="P40" s="97"/>
+      <c r="Q40" s="97"/>
+      <c r="R40" s="98"/>
+    </row>
+    <row r="41" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F41" s="96"/>
+      <c r="G41" s="97"/>
+      <c r="H41" s="97"/>
+      <c r="I41" s="97"/>
+      <c r="J41" s="97"/>
+      <c r="K41" s="97"/>
+      <c r="L41" s="97"/>
+      <c r="M41" s="97"/>
+      <c r="N41" s="97"/>
+      <c r="O41" s="97"/>
+      <c r="P41" s="97"/>
+      <c r="Q41" s="97"/>
+      <c r="R41" s="98"/>
+    </row>
+    <row r="42" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F42" s="96"/>
+      <c r="G42" s="97"/>
+      <c r="H42" s="97"/>
+      <c r="I42" s="97"/>
+      <c r="J42" s="97"/>
+      <c r="K42" s="97"/>
+      <c r="L42" s="97"/>
+      <c r="M42" s="97"/>
+      <c r="N42" s="97"/>
+      <c r="O42" s="97"/>
+      <c r="P42" s="97"/>
+      <c r="Q42" s="97"/>
+      <c r="R42" s="98"/>
+    </row>
+    <row r="43" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F43" s="96"/>
+      <c r="G43" s="97"/>
+      <c r="H43" s="97"/>
+      <c r="I43" s="97"/>
+      <c r="J43" s="97"/>
+      <c r="K43" s="97"/>
+      <c r="L43" s="97"/>
+      <c r="M43" s="97"/>
+      <c r="N43" s="97"/>
+      <c r="O43" s="97"/>
+      <c r="P43" s="97"/>
+      <c r="Q43" s="97"/>
+      <c r="R43" s="98"/>
+    </row>
+    <row r="44" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F44" s="96"/>
+      <c r="G44" s="97"/>
+      <c r="H44" s="97"/>
+      <c r="I44" s="97"/>
+      <c r="J44" s="97"/>
+      <c r="K44" s="97"/>
+      <c r="L44" s="97"/>
+      <c r="M44" s="97"/>
+      <c r="N44" s="97"/>
+      <c r="O44" s="97"/>
+      <c r="P44" s="97"/>
+      <c r="Q44" s="97"/>
+      <c r="R44" s="98"/>
+    </row>
+    <row r="45" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F45" s="96"/>
+      <c r="G45" s="97"/>
+      <c r="H45" s="97"/>
+      <c r="I45" s="97"/>
+      <c r="J45" s="97"/>
+      <c r="K45" s="97"/>
+      <c r="L45" s="97"/>
+      <c r="M45" s="97"/>
+      <c r="N45" s="97"/>
+      <c r="O45" s="97"/>
+      <c r="P45" s="97"/>
+      <c r="Q45" s="97"/>
+      <c r="R45" s="98"/>
+    </row>
+    <row r="46" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F46" s="99"/>
+      <c r="G46" s="100"/>
+      <c r="H46" s="100"/>
+      <c r="I46" s="100"/>
+      <c r="J46" s="100"/>
+      <c r="K46" s="100"/>
+      <c r="L46" s="100"/>
+      <c r="M46" s="100"/>
+      <c r="N46" s="100"/>
+      <c r="O46" s="100"/>
+      <c r="P46" s="100"/>
+      <c r="Q46" s="100"/>
+      <c r="R46" s="101"/>
+    </row>
+    <row r="81" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D81" s="83" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D82" s="83"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D83" s="83"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D84" s="83"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D85" s="83"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D86" s="83"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D87" s="83"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D88" s="83"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D89" s="83"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D90" s="83"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D91" s="83"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B93" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C93" s="20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B94" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B95" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C95" s="20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B96" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B97" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C97" s="20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B98" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C98" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B99" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C99" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B100" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C100" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C105" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B106" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C106" s="20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B107" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C107" s="20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B108" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C108" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B109" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C109" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B110" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C110" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B111" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C111" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B112" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C112" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B117" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C117" s="20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B118" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C118" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B119" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C119" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B120" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C120" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B121" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C121" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B122" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C122" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B124" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C124" s="20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B125" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C125" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B126" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C126" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B127" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C127" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B128" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C128" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B129" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C129" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B131" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C131" s="20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B132" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C132" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B133" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C133" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B134" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C134" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B135" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C135" s="20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B136" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C136" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B138" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C138" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B139" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C139" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B140" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C140" s="20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B141" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C141" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B152" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C152" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B153" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C153" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B154" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C154" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B155" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C155" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B168" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C168" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B169" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C169" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B171" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C171" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B172" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C172" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B174" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C174" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B175" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C175" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B177" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C177" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B178" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C178" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B180" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C180" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B181" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C181" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F21:R21"/>
+    <mergeCell ref="D81:D91"/>
+    <mergeCell ref="F15:R17"/>
+    <mergeCell ref="F2:R4"/>
+    <mergeCell ref="F27:R46"/>
+  </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3942,1205 +5149,6 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R181"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="49.625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="60.75" style="20" customWidth="1"/>
-    <col min="4" max="13" width="9" style="21"/>
-    <col min="14" max="14" width="9" style="21" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-    </row>
-    <row r="2" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="F2" s="84" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="86"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F3" s="87"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="89"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F4" s="90"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="92"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="25"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-    </row>
-    <row r="15" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F15" s="84" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="85"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="85"/>
-      <c r="J15" s="85"/>
-      <c r="K15" s="85"/>
-      <c r="L15" s="85"/>
-      <c r="M15" s="85"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="85"/>
-      <c r="P15" s="85"/>
-      <c r="Q15" s="85"/>
-      <c r="R15" s="86"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F16" s="87"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="88"/>
-      <c r="I16" s="88"/>
-      <c r="J16" s="88"/>
-      <c r="K16" s="88"/>
-      <c r="L16" s="88"/>
-      <c r="M16" s="88"/>
-      <c r="N16" s="88"/>
-      <c r="O16" s="88"/>
-      <c r="P16" s="88"/>
-      <c r="Q16" s="88"/>
-      <c r="R16" s="89"/>
-    </row>
-    <row r="17" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F17" s="90"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="91"/>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="92"/>
-    </row>
-    <row r="18" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
-    </row>
-    <row r="19" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="26"/>
-    </row>
-    <row r="21" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F21" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="81"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="81"/>
-      <c r="R21" s="82"/>
-    </row>
-    <row r="27" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F27" s="93" t="s">
-        <v>36</v>
-      </c>
-      <c r="G27" s="94"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="94"/>
-      <c r="J27" s="94"/>
-      <c r="K27" s="94"/>
-      <c r="L27" s="94"/>
-      <c r="M27" s="94"/>
-      <c r="N27" s="94"/>
-      <c r="O27" s="94"/>
-      <c r="P27" s="94"/>
-      <c r="Q27" s="94"/>
-      <c r="R27" s="95"/>
-    </row>
-    <row r="28" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F28" s="96"/>
-      <c r="G28" s="97"/>
-      <c r="H28" s="97"/>
-      <c r="I28" s="97"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="97"/>
-      <c r="L28" s="97"/>
-      <c r="M28" s="97"/>
-      <c r="N28" s="97"/>
-      <c r="O28" s="97"/>
-      <c r="P28" s="97"/>
-      <c r="Q28" s="97"/>
-      <c r="R28" s="98"/>
-    </row>
-    <row r="29" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F29" s="96"/>
-      <c r="G29" s="97"/>
-      <c r="H29" s="97"/>
-      <c r="I29" s="97"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="97"/>
-      <c r="L29" s="97"/>
-      <c r="M29" s="97"/>
-      <c r="N29" s="97"/>
-      <c r="O29" s="97"/>
-      <c r="P29" s="97"/>
-      <c r="Q29" s="97"/>
-      <c r="R29" s="98"/>
-    </row>
-    <row r="30" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F30" s="96"/>
-      <c r="G30" s="97"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="97"/>
-      <c r="J30" s="97"/>
-      <c r="K30" s="97"/>
-      <c r="L30" s="97"/>
-      <c r="M30" s="97"/>
-      <c r="N30" s="97"/>
-      <c r="O30" s="97"/>
-      <c r="P30" s="97"/>
-      <c r="Q30" s="97"/>
-      <c r="R30" s="98"/>
-    </row>
-    <row r="31" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F31" s="96"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="97"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="97"/>
-      <c r="K31" s="97"/>
-      <c r="L31" s="97"/>
-      <c r="M31" s="97"/>
-      <c r="N31" s="97"/>
-      <c r="O31" s="97"/>
-      <c r="P31" s="97"/>
-      <c r="Q31" s="97"/>
-      <c r="R31" s="98"/>
-    </row>
-    <row r="32" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F32" s="96"/>
-      <c r="G32" s="97"/>
-      <c r="H32" s="97"/>
-      <c r="I32" s="97"/>
-      <c r="J32" s="97"/>
-      <c r="K32" s="97"/>
-      <c r="L32" s="97"/>
-      <c r="M32" s="97"/>
-      <c r="N32" s="97"/>
-      <c r="O32" s="97"/>
-      <c r="P32" s="97"/>
-      <c r="Q32" s="97"/>
-      <c r="R32" s="98"/>
-    </row>
-    <row r="33" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F33" s="96"/>
-      <c r="G33" s="97"/>
-      <c r="H33" s="97"/>
-      <c r="I33" s="97"/>
-      <c r="J33" s="97"/>
-      <c r="K33" s="97"/>
-      <c r="L33" s="97"/>
-      <c r="M33" s="97"/>
-      <c r="N33" s="97"/>
-      <c r="O33" s="97"/>
-      <c r="P33" s="97"/>
-      <c r="Q33" s="97"/>
-      <c r="R33" s="98"/>
-    </row>
-    <row r="34" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F34" s="96"/>
-      <c r="G34" s="97"/>
-      <c r="H34" s="97"/>
-      <c r="I34" s="97"/>
-      <c r="J34" s="97"/>
-      <c r="K34" s="97"/>
-      <c r="L34" s="97"/>
-      <c r="M34" s="97"/>
-      <c r="N34" s="97"/>
-      <c r="O34" s="97"/>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="98"/>
-    </row>
-    <row r="35" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F35" s="96"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="97"/>
-      <c r="J35" s="97"/>
-      <c r="K35" s="97"/>
-      <c r="L35" s="97"/>
-      <c r="M35" s="97"/>
-      <c r="N35" s="97"/>
-      <c r="O35" s="97"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="97"/>
-      <c r="R35" s="98"/>
-    </row>
-    <row r="36" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F36" s="96"/>
-      <c r="G36" s="97"/>
-      <c r="H36" s="97"/>
-      <c r="I36" s="97"/>
-      <c r="J36" s="97"/>
-      <c r="K36" s="97"/>
-      <c r="L36" s="97"/>
-      <c r="M36" s="97"/>
-      <c r="N36" s="97"/>
-      <c r="O36" s="97"/>
-      <c r="P36" s="97"/>
-      <c r="Q36" s="97"/>
-      <c r="R36" s="98"/>
-    </row>
-    <row r="37" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F37" s="96"/>
-      <c r="G37" s="97"/>
-      <c r="H37" s="97"/>
-      <c r="I37" s="97"/>
-      <c r="J37" s="97"/>
-      <c r="K37" s="97"/>
-      <c r="L37" s="97"/>
-      <c r="M37" s="97"/>
-      <c r="N37" s="97"/>
-      <c r="O37" s="97"/>
-      <c r="P37" s="97"/>
-      <c r="Q37" s="97"/>
-      <c r="R37" s="98"/>
-    </row>
-    <row r="38" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F38" s="96"/>
-      <c r="G38" s="97"/>
-      <c r="H38" s="97"/>
-      <c r="I38" s="97"/>
-      <c r="J38" s="97"/>
-      <c r="K38" s="97"/>
-      <c r="L38" s="97"/>
-      <c r="M38" s="97"/>
-      <c r="N38" s="97"/>
-      <c r="O38" s="97"/>
-      <c r="P38" s="97"/>
-      <c r="Q38" s="97"/>
-      <c r="R38" s="98"/>
-    </row>
-    <row r="39" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F39" s="96"/>
-      <c r="G39" s="97"/>
-      <c r="H39" s="97"/>
-      <c r="I39" s="97"/>
-      <c r="J39" s="97"/>
-      <c r="K39" s="97"/>
-      <c r="L39" s="97"/>
-      <c r="M39" s="97"/>
-      <c r="N39" s="97"/>
-      <c r="O39" s="97"/>
-      <c r="P39" s="97"/>
-      <c r="Q39" s="97"/>
-      <c r="R39" s="98"/>
-    </row>
-    <row r="40" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F40" s="96"/>
-      <c r="G40" s="97"/>
-      <c r="H40" s="97"/>
-      <c r="I40" s="97"/>
-      <c r="J40" s="97"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="97"/>
-      <c r="M40" s="97"/>
-      <c r="N40" s="97"/>
-      <c r="O40" s="97"/>
-      <c r="P40" s="97"/>
-      <c r="Q40" s="97"/>
-      <c r="R40" s="98"/>
-    </row>
-    <row r="41" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F41" s="96"/>
-      <c r="G41" s="97"/>
-      <c r="H41" s="97"/>
-      <c r="I41" s="97"/>
-      <c r="J41" s="97"/>
-      <c r="K41" s="97"/>
-      <c r="L41" s="97"/>
-      <c r="M41" s="97"/>
-      <c r="N41" s="97"/>
-      <c r="O41" s="97"/>
-      <c r="P41" s="97"/>
-      <c r="Q41" s="97"/>
-      <c r="R41" s="98"/>
-    </row>
-    <row r="42" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F42" s="96"/>
-      <c r="G42" s="97"/>
-      <c r="H42" s="97"/>
-      <c r="I42" s="97"/>
-      <c r="J42" s="97"/>
-      <c r="K42" s="97"/>
-      <c r="L42" s="97"/>
-      <c r="M42" s="97"/>
-      <c r="N42" s="97"/>
-      <c r="O42" s="97"/>
-      <c r="P42" s="97"/>
-      <c r="Q42" s="97"/>
-      <c r="R42" s="98"/>
-    </row>
-    <row r="43" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F43" s="96"/>
-      <c r="G43" s="97"/>
-      <c r="H43" s="97"/>
-      <c r="I43" s="97"/>
-      <c r="J43" s="97"/>
-      <c r="K43" s="97"/>
-      <c r="L43" s="97"/>
-      <c r="M43" s="97"/>
-      <c r="N43" s="97"/>
-      <c r="O43" s="97"/>
-      <c r="P43" s="97"/>
-      <c r="Q43" s="97"/>
-      <c r="R43" s="98"/>
-    </row>
-    <row r="44" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F44" s="96"/>
-      <c r="G44" s="97"/>
-      <c r="H44" s="97"/>
-      <c r="I44" s="97"/>
-      <c r="J44" s="97"/>
-      <c r="K44" s="97"/>
-      <c r="L44" s="97"/>
-      <c r="M44" s="97"/>
-      <c r="N44" s="97"/>
-      <c r="O44" s="97"/>
-      <c r="P44" s="97"/>
-      <c r="Q44" s="97"/>
-      <c r="R44" s="98"/>
-    </row>
-    <row r="45" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F45" s="96"/>
-      <c r="G45" s="97"/>
-      <c r="H45" s="97"/>
-      <c r="I45" s="97"/>
-      <c r="J45" s="97"/>
-      <c r="K45" s="97"/>
-      <c r="L45" s="97"/>
-      <c r="M45" s="97"/>
-      <c r="N45" s="97"/>
-      <c r="O45" s="97"/>
-      <c r="P45" s="97"/>
-      <c r="Q45" s="97"/>
-      <c r="R45" s="98"/>
-    </row>
-    <row r="46" spans="6:18" x14ac:dyDescent="0.3">
-      <c r="F46" s="99"/>
-      <c r="G46" s="100"/>
-      <c r="H46" s="100"/>
-      <c r="I46" s="100"/>
-      <c r="J46" s="100"/>
-      <c r="K46" s="100"/>
-      <c r="L46" s="100"/>
-      <c r="M46" s="100"/>
-      <c r="N46" s="100"/>
-      <c r="O46" s="100"/>
-      <c r="P46" s="100"/>
-      <c r="Q46" s="100"/>
-      <c r="R46" s="101"/>
-    </row>
-    <row r="81" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D81" s="83" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D82" s="83"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D83" s="83"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D84" s="83"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D85" s="83"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D86" s="83"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D87" s="83"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D88" s="83"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D89" s="83"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D90" s="83"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D91" s="83"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B93" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C93" s="20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B94" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C94" s="20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B95" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B96" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C96" s="20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B97" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C97" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B98" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C98" s="20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B99" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C99" s="20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B100" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C100" s="20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B105" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C105" s="20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B106" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C106" s="20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B107" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C107" s="20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B108" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C108" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B109" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C109" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B110" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C110" s="20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B111" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C111" s="20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B112" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B117" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C117" s="20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B118" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C118" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B119" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C119" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B120" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C120" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B121" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C121" s="20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B122" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C122" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B124" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C124" s="20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B125" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C125" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B126" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C126" s="20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B127" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C127" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B128" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C128" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B129" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C129" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B131" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C131" s="20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B132" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C132" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B133" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C133" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B134" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C134" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B135" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C135" s="20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B136" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C136" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B138" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C138" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B139" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C139" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B140" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C140" s="20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B141" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C141" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B152" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C152" s="20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B153" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C153" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B154" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C154" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B155" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C155" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B168" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C168" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B169" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C169" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B171" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C171" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B172" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C172" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B174" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C174" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B175" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C175" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A177" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B177" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C177" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A178" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B178" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C178" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A180" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B180" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C180" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B181" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C181" s="20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F21:R21"/>
-    <mergeCell ref="D81:D91"/>
-    <mergeCell ref="F15:R17"/>
-    <mergeCell ref="F2:R4"/>
-    <mergeCell ref="F27:R46"/>
-  </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12237,10 +12245,10 @@
     </row>
     <row r="52" spans="1:8" s="67" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A52" s="129" t="s">
-        <v>552</v>
+        <v>601</v>
       </c>
       <c r="B52" s="129" t="s">
-        <v>553</v>
+        <v>602</v>
       </c>
       <c r="C52" s="130" t="s">
         <v>109</v>

--- a/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0B(杨文成 20260509).xlsx
+++ b/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0B(杨文成 20260509).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LinWenTao\Desktop\Outbound_station\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F9280E-A508-4AD0-A7C0-315F3235DD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5B099E-7096-43F9-9D91-1F3D48493DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="版本" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="644">
   <si>
     <t>版本</t>
   </si>
@@ -2477,6 +2477,10 @@
   </si>
   <si>
     <t>total_packages</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>协议当中有涉及到列表的内容，列表统一规定为从左到右，从下到上顺序</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -2802,7 +2806,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3016,20 +3020,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3043,30 +3051,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3077,9 +3085,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3096,6 +3101,18 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3105,6 +3122,46 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3141,60 +3198,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3715,7 +3720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
@@ -3729,50 +3734,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
     </row>
     <row r="2" spans="1:8" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
     </row>
     <row r="4" spans="1:8" ht="130.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
       <c r="G4" s="21" t="s">
         <v>11</v>
       </c>
@@ -3781,14 +3786,14 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="87" t="s">
         <v>469</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
       <c r="G5" s="21" t="s">
         <v>466</v>
       </c>
@@ -3796,229 +3801,231 @@
         <v>501</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
+    <row r="6" spans="1:8" s="49" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="87" t="s">
+        <v>643</v>
+      </c>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
     </row>
-    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="94" t="s">
+    <row r="7" spans="1:8" s="83" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
-      <c r="B8" s="88" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="89"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="20"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="20"/>
-      <c r="B9" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="89" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="90"/>
+      <c r="B9" s="90" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="92"/>
       <c r="G9" s="22"/>
       <c r="H9" s="20"/>
     </row>
-    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="20"/>
-      <c r="B10" s="59" t="s">
-        <v>471</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>472</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>19</v>
+      <c r="B10" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="E10" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="86"/>
+        <v>18</v>
+      </c>
+      <c r="F10" s="92"/>
       <c r="G10" s="22"/>
       <c r="H10" s="20"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="20"/>
-      <c r="B11" s="48" t="s">
-        <v>473</v>
-      </c>
-      <c r="C11" s="26">
-        <v>1</v>
-      </c>
-      <c r="D11" s="25" t="s">
+      <c r="B11" s="59" t="s">
+        <v>471</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>472</v>
+      </c>
+      <c r="D11" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="91" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="86"/>
+      <c r="E11" s="93" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="94"/>
       <c r="G11" s="22"/>
       <c r="H11" s="20"/>
     </row>
-    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="20"/>
-      <c r="B12" s="59" t="s">
-        <v>474</v>
-      </c>
-      <c r="C12" s="25"/>
+      <c r="B12" s="48" t="s">
+        <v>473</v>
+      </c>
+      <c r="C12" s="26">
+        <v>1</v>
+      </c>
       <c r="D12" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="91" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="86"/>
+        <v>19</v>
+      </c>
+      <c r="E12" s="93" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="94"/>
       <c r="G12" s="22"/>
       <c r="H12" s="20"/>
     </row>
-    <row r="13" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="20"/>
-      <c r="B13" s="48" t="s">
-        <v>475</v>
+      <c r="B13" s="59" t="s">
+        <v>474</v>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="85" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="86"/>
+      <c r="E13" s="93" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="94"/>
       <c r="G13" s="22"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="20"/>
       <c r="B14" s="48" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="86"/>
+        <v>23</v>
+      </c>
+      <c r="E14" s="96" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="94"/>
       <c r="G14" s="22"/>
       <c r="H14" s="20"/>
     </row>
-    <row r="15" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="20"/>
       <c r="B15" s="48" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="85" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="86"/>
+        <v>26</v>
+      </c>
+      <c r="E15" s="96" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="94"/>
       <c r="G15" s="22"/>
       <c r="H15" s="20"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
+      <c r="B16" s="48" t="s">
+        <v>477</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="94"/>
+      <c r="G16" s="22"/>
       <c r="H16" s="20"/>
     </row>
-    <row r="17" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="87" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+    </row>
+    <row r="18" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="97" t="s">
         <v>478</v>
       </c>
-      <c r="B17" s="87"/>
-      <c r="C17" s="87"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="87"/>
-      <c r="H17" s="20"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="97"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
     </row>
-    <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="83"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
-      <c r="H20" s="29"/>
+      <c r="H20" s="20"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
+      <c r="A21" s="95"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="95"/>
+      <c r="D21" s="95"/>
+      <c r="E21" s="95"/>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
-      <c r="H21" s="31"/>
+      <c r="H21" s="29"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="32"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
-      <c r="H22" s="36"/>
+      <c r="H22" s="31"/>
     </row>
     <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="32"/>
@@ -4050,15 +4057,15 @@
       <c r="G25" s="20"/>
       <c r="H25" s="36"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
+    <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="32"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="35"/>
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
+      <c r="H26" s="36"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="27"/>
@@ -4070,32 +4077,32 @@
       <c r="G27" s="20"/>
       <c r="H27" s="20"/>
     </row>
-    <row r="28" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A28" s="83"/>
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="27"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
       <c r="H28" s="20"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="30"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
+      <c r="A29" s="95"/>
+      <c r="B29" s="95"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
     </row>
     <row r="30" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="35"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
@@ -4141,24 +4148,24 @@
       <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A35" s="35"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="32"/>
       <c r="C35" s="33"/>
       <c r="D35" s="34"/>
       <c r="E35" s="35"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
     </row>
     <row r="36" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A36" s="32"/>
+      <c r="A36" s="35"/>
       <c r="B36" s="32"/>
       <c r="C36" s="33"/>
       <c r="D36" s="34"/>
       <c r="E36" s="35"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
     </row>
     <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A37" s="32"/>
@@ -4170,12 +4177,12 @@
       <c r="G37" s="20"/>
       <c r="H37" s="20"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="20"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
+    <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="32"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="35"/>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
       <c r="H38" s="20"/>
@@ -4191,35 +4198,46 @@
       <c r="H39" s="20"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="84"/>
-      <c r="B40" s="84"/>
-      <c r="C40" s="84"/>
-      <c r="D40" s="84"/>
-      <c r="E40" s="84"/>
-      <c r="F40" s="84"/>
-      <c r="G40" s="84"/>
-      <c r="H40" s="84"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="88"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4252,11 +4270,11 @@
       <c r="B2" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="19">
@@ -4265,11 +4283,11 @@
       <c r="B3" s="19">
         <v>11000</v>
       </c>
-      <c r="C3" s="96" t="s">
+      <c r="C3" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="19">
@@ -4278,11 +4296,11 @@
       <c r="B4" s="19">
         <v>11001</v>
       </c>
-      <c r="C4" s="96" t="s">
+      <c r="C4" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="19">
@@ -4291,11 +4309,11 @@
       <c r="B5" s="19">
         <v>11002</v>
       </c>
-      <c r="C5" s="96" t="s">
+      <c r="C5" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
@@ -4304,11 +4322,11 @@
       <c r="B6" s="19">
         <v>11003</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
@@ -4317,11 +4335,11 @@
       <c r="B7" s="19">
         <v>11004</v>
       </c>
-      <c r="C7" s="96" t="s">
+      <c r="C7" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
@@ -4330,11 +4348,11 @@
       <c r="B8" s="19">
         <v>11005</v>
       </c>
-      <c r="C8" s="96" t="s">
+      <c r="C8" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
@@ -4343,11 +4361,11 @@
       <c r="B9" s="19">
         <v>11006</v>
       </c>
-      <c r="C9" s="95" t="s">
+      <c r="C9" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
@@ -4356,20 +4374,20 @@
       <c r="B10" s="19">
         <v>11007</v>
       </c>
-      <c r="C10" s="95" t="s">
+      <c r="C10" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="97" t="s">
+      <c r="A13" s="101" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="97"/>
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="97"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
@@ -4379,11 +4397,11 @@
         <f t="shared" ref="B14:B15" si="0">A14+10000</f>
         <v>11100</v>
       </c>
-      <c r="C14" s="84" t="s">
+      <c r="C14" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
     </row>
     <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -4393,11 +4411,11 @@
         <f t="shared" si="0"/>
         <v>11101</v>
       </c>
-      <c r="C15" s="84" t="s">
+      <c r="C15" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="98" t="s">
@@ -4415,11 +4433,11 @@
       <c r="B19" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="84" t="s">
+      <c r="C19" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="19">
@@ -4428,11 +4446,11 @@
       <c r="B20" s="19">
         <v>12000</v>
       </c>
-      <c r="C20" s="96" t="s">
+      <c r="C20" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="19">
@@ -4441,11 +4459,11 @@
       <c r="B21" s="19">
         <v>12001</v>
       </c>
-      <c r="C21" s="95" t="s">
+      <c r="C21" s="100" t="s">
         <v>266</v>
       </c>
-      <c r="D21" s="95"/>
-      <c r="E21" s="95"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="100"/>
     </row>
     <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4474,16 +4492,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A13:E13"/>
@@ -4491,6 +4499,16 @@
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4511,16 +4529,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -4652,7 +4670,7 @@
         <v>64</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>54</v>
+        <v>278</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>641</v>
@@ -4677,16 +4695,16 @@
     </row>
     <row r="11" spans="1:8" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="97" t="s">
         <v>246</v>
       </c>
-      <c r="B13" s="84"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="88"/>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -4774,13 +4792,13 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="99" t="s">
+      <c r="A19" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="99"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
@@ -4851,13 +4869,13 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="100" t="s">
+      <c r="A26" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="100"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
+      <c r="B26" s="112"/>
+      <c r="C26" s="112"/>
+      <c r="D26" s="112"/>
+      <c r="E26" s="112"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -5005,16 +5023,16 @@
       <c r="E36" s="17"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="84" t="s">
+      <c r="A37" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="84"/>
-      <c r="C37" s="84"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
+      <c r="B37" s="88"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="88"/>
     </row>
     <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
@@ -5081,16 +5099,16 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="84" t="s">
+      <c r="A48" s="88" t="s">
         <v>115</v>
       </c>
-      <c r="B48" s="84"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="84"/>
-      <c r="E48" s="84"/>
-      <c r="F48" s="84"/>
-      <c r="G48" s="84"/>
-      <c r="H48" s="84"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="88"/>
+      <c r="D48" s="88"/>
+      <c r="E48" s="88"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="88"/>
+      <c r="H48" s="88"/>
     </row>
     <row r="49" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
@@ -5247,16 +5265,16 @@
     </row>
     <row r="58" spans="1:8" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="60" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="87" t="s">
+      <c r="A60" s="97" t="s">
         <v>214</v>
       </c>
-      <c r="B60" s="84"/>
-      <c r="C60" s="84"/>
-      <c r="D60" s="84"/>
-      <c r="E60" s="84"/>
-      <c r="F60" s="84"/>
-      <c r="G60" s="84"/>
-      <c r="H60" s="84"/>
+      <c r="B60" s="88"/>
+      <c r="C60" s="88"/>
+      <c r="D60" s="88"/>
+      <c r="E60" s="88"/>
+      <c r="F60" s="88"/>
+      <c r="G60" s="88"/>
+      <c r="H60" s="88"/>
     </row>
     <row r="61" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
@@ -5344,13 +5362,13 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A66" s="99" t="s">
+      <c r="A66" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="B66" s="99"/>
-      <c r="C66" s="99"/>
-      <c r="D66" s="99"/>
-      <c r="E66" s="99"/>
+      <c r="B66" s="103"/>
+      <c r="C66" s="103"/>
+      <c r="D66" s="103"/>
+      <c r="E66" s="103"/>
     </row>
     <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
@@ -5421,13 +5439,13 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="100" t="s">
+      <c r="A73" s="112" t="s">
         <v>117</v>
       </c>
-      <c r="B73" s="100"/>
-      <c r="C73" s="100"/>
-      <c r="D73" s="100"/>
-      <c r="E73" s="100"/>
+      <c r="B73" s="112"/>
+      <c r="C73" s="112"/>
+      <c r="D73" s="112"/>
+      <c r="E73" s="112"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -5649,13 +5667,13 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="100" t="s">
+      <c r="A94" s="112" t="s">
         <v>123</v>
       </c>
-      <c r="B94" s="100"/>
-      <c r="C94" s="100"/>
-      <c r="D94" s="100"/>
-      <c r="E94" s="100"/>
+      <c r="B94" s="112"/>
+      <c r="C94" s="112"/>
+      <c r="D94" s="112"/>
+      <c r="E94" s="112"/>
     </row>
     <row r="95" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
@@ -5794,13 +5812,13 @@
       </c>
     </row>
     <row r="103" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A103" s="99" t="s">
+      <c r="A103" s="103" t="s">
         <v>136</v>
       </c>
-      <c r="B103" s="99"/>
-      <c r="C103" s="99"/>
-      <c r="D103" s="99"/>
-      <c r="E103" s="99"/>
+      <c r="B103" s="103"/>
+      <c r="C103" s="103"/>
+      <c r="D103" s="103"/>
+      <c r="E103" s="103"/>
     </row>
     <row r="104" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A104" s="6" t="s">
@@ -5888,13 +5906,13 @@
       </c>
     </row>
     <row r="109" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A109" s="99" t="s">
+      <c r="A109" s="103" t="s">
         <v>148</v>
       </c>
-      <c r="B109" s="99"/>
-      <c r="C109" s="99"/>
-      <c r="D109" s="99"/>
-      <c r="E109" s="99"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="103"/>
+      <c r="D109" s="103"/>
+      <c r="E109" s="103"/>
     </row>
     <row r="110" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
@@ -5912,14 +5930,14 @@
       <c r="E110" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F110" s="105" t="s">
+      <c r="F110" s="113" t="s">
         <v>149</v>
       </c>
-      <c r="G110" s="105"/>
-      <c r="H110" s="105"/>
-      <c r="I110" s="105"/>
-      <c r="J110" s="105"/>
-      <c r="K110" s="105"/>
+      <c r="G110" s="113"/>
+      <c r="H110" s="113"/>
+      <c r="I110" s="113"/>
+      <c r="J110" s="113"/>
+      <c r="K110" s="113"/>
     </row>
     <row r="111" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
@@ -5973,13 +5991,13 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="102" t="s">
+      <c r="A114" s="104" t="s">
         <v>449</v>
       </c>
-      <c r="B114" s="103"/>
-      <c r="C114" s="103"/>
-      <c r="D114" s="103"/>
-      <c r="E114" s="104"/>
+      <c r="B114" s="105"/>
+      <c r="C114" s="105"/>
+      <c r="D114" s="105"/>
+      <c r="E114" s="106"/>
     </row>
     <row r="115" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
@@ -6226,13 +6244,13 @@
       <c r="E137" s="17"/>
     </row>
     <row r="138" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A138" s="101" t="s">
+      <c r="A138" s="102" t="s">
         <v>305</v>
       </c>
-      <c r="B138" s="99"/>
-      <c r="C138" s="99"/>
-      <c r="D138" s="99"/>
-      <c r="E138" s="99"/>
+      <c r="B138" s="103"/>
+      <c r="C138" s="103"/>
+      <c r="D138" s="103"/>
+      <c r="E138" s="103"/>
     </row>
     <row r="139" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
@@ -6303,13 +6321,13 @@
       </c>
     </row>
     <row r="143" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A143" s="101" t="s">
+      <c r="A143" s="102" t="s">
         <v>290</v>
       </c>
-      <c r="B143" s="99"/>
-      <c r="C143" s="99"/>
-      <c r="D143" s="99"/>
-      <c r="E143" s="99"/>
+      <c r="B143" s="103"/>
+      <c r="C143" s="103"/>
+      <c r="D143" s="103"/>
+      <c r="E143" s="103"/>
     </row>
     <row r="144" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A144" s="6" t="s">
@@ -6397,13 +6415,13 @@
       </c>
     </row>
     <row r="149" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A149" s="106" t="s">
+      <c r="A149" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="B149" s="107"/>
-      <c r="C149" s="107"/>
-      <c r="D149" s="107"/>
-      <c r="E149" s="108"/>
+      <c r="B149" s="108"/>
+      <c r="C149" s="108"/>
+      <c r="D149" s="108"/>
+      <c r="E149" s="109"/>
     </row>
     <row r="150" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A150" s="6" t="s">
@@ -6475,13 +6493,13 @@
       </c>
     </row>
     <row r="156" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A156" s="101" t="s">
+      <c r="A156" s="102" t="s">
         <v>304</v>
       </c>
-      <c r="B156" s="99"/>
-      <c r="C156" s="99"/>
-      <c r="D156" s="99"/>
-      <c r="E156" s="99"/>
+      <c r="B156" s="103"/>
+      <c r="C156" s="103"/>
+      <c r="D156" s="103"/>
+      <c r="E156" s="103"/>
     </row>
     <row r="157" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A157" s="6" t="s">
@@ -6569,13 +6587,13 @@
       </c>
     </row>
     <row r="162" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A162" s="101" t="s">
+      <c r="A162" s="102" t="s">
         <v>306</v>
       </c>
-      <c r="B162" s="99"/>
-      <c r="C162" s="99"/>
-      <c r="D162" s="99"/>
-      <c r="E162" s="99"/>
+      <c r="B162" s="103"/>
+      <c r="C162" s="103"/>
+      <c r="D162" s="103"/>
+      <c r="E162" s="103"/>
     </row>
     <row r="163" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A163" s="6" t="s">
@@ -6638,83 +6656,83 @@
     <row r="167" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="168" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="169" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="109" t="s">
+      <c r="A169" s="110" t="s">
         <v>318</v>
       </c>
-      <c r="B169" s="110"/>
-      <c r="C169" s="110"/>
-      <c r="D169" s="110"/>
-      <c r="E169" s="110"/>
+      <c r="B169" s="111"/>
+      <c r="C169" s="111"/>
+      <c r="D169" s="111"/>
+      <c r="E169" s="111"/>
     </row>
     <row r="170" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="110"/>
-      <c r="B170" s="110"/>
-      <c r="C170" s="110"/>
-      <c r="D170" s="110"/>
-      <c r="E170" s="110"/>
+      <c r="A170" s="111"/>
+      <c r="B170" s="111"/>
+      <c r="C170" s="111"/>
+      <c r="D170" s="111"/>
+      <c r="E170" s="111"/>
     </row>
     <row r="171" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="110"/>
-      <c r="B171" s="110"/>
-      <c r="C171" s="110"/>
-      <c r="D171" s="110"/>
-      <c r="E171" s="110"/>
+      <c r="A171" s="111"/>
+      <c r="B171" s="111"/>
+      <c r="C171" s="111"/>
+      <c r="D171" s="111"/>
+      <c r="E171" s="111"/>
     </row>
     <row r="172" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="110"/>
-      <c r="B172" s="110"/>
-      <c r="C172" s="110"/>
-      <c r="D172" s="110"/>
-      <c r="E172" s="110"/>
+      <c r="A172" s="111"/>
+      <c r="B172" s="111"/>
+      <c r="C172" s="111"/>
+      <c r="D172" s="111"/>
+      <c r="E172" s="111"/>
     </row>
     <row r="173" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="110"/>
-      <c r="B173" s="110"/>
-      <c r="C173" s="110"/>
-      <c r="D173" s="110"/>
-      <c r="E173" s="110"/>
+      <c r="A173" s="111"/>
+      <c r="B173" s="111"/>
+      <c r="C173" s="111"/>
+      <c r="D173" s="111"/>
+      <c r="E173" s="111"/>
     </row>
     <row r="174" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="110"/>
-      <c r="B174" s="110"/>
-      <c r="C174" s="110"/>
-      <c r="D174" s="110"/>
-      <c r="E174" s="110"/>
+      <c r="A174" s="111"/>
+      <c r="B174" s="111"/>
+      <c r="C174" s="111"/>
+      <c r="D174" s="111"/>
+      <c r="E174" s="111"/>
     </row>
     <row r="175" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="110"/>
-      <c r="B175" s="110"/>
-      <c r="C175" s="110"/>
-      <c r="D175" s="110"/>
-      <c r="E175" s="110"/>
+      <c r="A175" s="111"/>
+      <c r="B175" s="111"/>
+      <c r="C175" s="111"/>
+      <c r="D175" s="111"/>
+      <c r="E175" s="111"/>
     </row>
     <row r="176" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="110"/>
-      <c r="B176" s="110"/>
-      <c r="C176" s="110"/>
-      <c r="D176" s="110"/>
-      <c r="E176" s="110"/>
+      <c r="A176" s="111"/>
+      <c r="B176" s="111"/>
+      <c r="C176" s="111"/>
+      <c r="D176" s="111"/>
+      <c r="E176" s="111"/>
     </row>
     <row r="177" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="110"/>
-      <c r="B177" s="110"/>
-      <c r="C177" s="110"/>
-      <c r="D177" s="110"/>
-      <c r="E177" s="110"/>
+      <c r="A177" s="111"/>
+      <c r="B177" s="111"/>
+      <c r="C177" s="111"/>
+      <c r="D177" s="111"/>
+      <c r="E177" s="111"/>
     </row>
     <row r="178" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="110"/>
-      <c r="B178" s="110"/>
-      <c r="C178" s="110"/>
-      <c r="D178" s="110"/>
-      <c r="E178" s="110"/>
+      <c r="A178" s="111"/>
+      <c r="B178" s="111"/>
+      <c r="C178" s="111"/>
+      <c r="D178" s="111"/>
+      <c r="E178" s="111"/>
     </row>
     <row r="179" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="110"/>
-      <c r="B179" s="110"/>
-      <c r="C179" s="110"/>
-      <c r="D179" s="110"/>
-      <c r="E179" s="110"/>
+      <c r="A179" s="111"/>
+      <c r="B179" s="111"/>
+      <c r="C179" s="111"/>
+      <c r="D179" s="111"/>
+      <c r="E179" s="111"/>
     </row>
     <row r="180" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="51"/>
@@ -6731,13 +6749,13 @@
       <c r="E181" s="51"/>
     </row>
     <row r="182" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="101" t="s">
+      <c r="A182" s="102" t="s">
         <v>319</v>
       </c>
-      <c r="B182" s="99"/>
-      <c r="C182" s="99"/>
-      <c r="D182" s="99"/>
-      <c r="E182" s="99"/>
+      <c r="B182" s="103"/>
+      <c r="C182" s="103"/>
+      <c r="D182" s="103"/>
+      <c r="E182" s="103"/>
     </row>
     <row r="183" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6" t="s">
@@ -6808,13 +6826,13 @@
       </c>
     </row>
     <row r="187" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="101" t="s">
+      <c r="A187" s="102" t="s">
         <v>325</v>
       </c>
-      <c r="B187" s="99"/>
-      <c r="C187" s="99"/>
-      <c r="D187" s="99"/>
-      <c r="E187" s="99"/>
+      <c r="B187" s="103"/>
+      <c r="C187" s="103"/>
+      <c r="D187" s="103"/>
+      <c r="E187" s="103"/>
     </row>
     <row r="188" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="6" t="s">
@@ -6851,13 +6869,13 @@
       </c>
     </row>
     <row r="190" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="99" t="s">
+      <c r="A190" s="103" t="s">
         <v>193</v>
       </c>
-      <c r="B190" s="99"/>
-      <c r="C190" s="99"/>
-      <c r="D190" s="99"/>
-      <c r="E190" s="99"/>
+      <c r="B190" s="103"/>
+      <c r="C190" s="103"/>
+      <c r="D190" s="103"/>
+      <c r="E190" s="103"/>
     </row>
     <row r="191" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
@@ -6979,13 +6997,13 @@
       </c>
     </row>
     <row r="198" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="101" t="s">
+      <c r="A198" s="102" t="s">
         <v>320</v>
       </c>
-      <c r="B198" s="99"/>
-      <c r="C198" s="99"/>
-      <c r="D198" s="99"/>
-      <c r="E198" s="99"/>
+      <c r="B198" s="103"/>
+      <c r="C198" s="103"/>
+      <c r="D198" s="103"/>
+      <c r="E198" s="103"/>
     </row>
     <row r="199" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6" t="s">
@@ -7073,13 +7091,13 @@
       </c>
     </row>
     <row r="204" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="101" t="s">
+      <c r="A204" s="102" t="s">
         <v>321</v>
       </c>
-      <c r="B204" s="99"/>
-      <c r="C204" s="99"/>
-      <c r="D204" s="99"/>
-      <c r="E204" s="99"/>
+      <c r="B204" s="103"/>
+      <c r="C204" s="103"/>
+      <c r="D204" s="103"/>
+      <c r="E204" s="103"/>
     </row>
     <row r="205" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="6" t="s">
@@ -7389,13 +7407,13 @@
       <c r="D227" s="12"/>
     </row>
     <row r="228" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A228" s="101" t="s">
+      <c r="A228" s="102" t="s">
         <v>399</v>
       </c>
-      <c r="B228" s="99"/>
-      <c r="C228" s="99"/>
-      <c r="D228" s="99"/>
-      <c r="E228" s="99"/>
+      <c r="B228" s="103"/>
+      <c r="C228" s="103"/>
+      <c r="D228" s="103"/>
+      <c r="E228" s="103"/>
     </row>
     <row r="229" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="6" t="s">
@@ -7466,13 +7484,13 @@
       </c>
     </row>
     <row r="233" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A233" s="101" t="s">
+      <c r="A233" s="102" t="s">
         <v>400</v>
       </c>
-      <c r="B233" s="99"/>
-      <c r="C233" s="99"/>
-      <c r="D233" s="99"/>
-      <c r="E233" s="99"/>
+      <c r="B233" s="103"/>
+      <c r="C233" s="103"/>
+      <c r="D233" s="103"/>
+      <c r="E233" s="103"/>
     </row>
     <row r="234" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="6" t="s">
@@ -7560,13 +7578,13 @@
       </c>
     </row>
     <row r="239" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="101" t="s">
+      <c r="A239" s="102" t="s">
         <v>406</v>
       </c>
-      <c r="B239" s="99"/>
-      <c r="C239" s="99"/>
-      <c r="D239" s="99"/>
-      <c r="E239" s="99"/>
+      <c r="B239" s="103"/>
+      <c r="C239" s="103"/>
+      <c r="D239" s="103"/>
+      <c r="E239" s="103"/>
     </row>
     <row r="240" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="6" t="s">
@@ -7653,13 +7671,13 @@
       <c r="D246" s="12"/>
     </row>
     <row r="247" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="101" t="s">
+      <c r="A247" s="102" t="s">
         <v>402</v>
       </c>
-      <c r="B247" s="99"/>
-      <c r="C247" s="99"/>
-      <c r="D247" s="99"/>
-      <c r="E247" s="99"/>
+      <c r="B247" s="103"/>
+      <c r="C247" s="103"/>
+      <c r="D247" s="103"/>
+      <c r="E247" s="103"/>
     </row>
     <row r="248" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="6" t="s">
@@ -7730,13 +7748,13 @@
       </c>
     </row>
     <row r="252" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="101" t="s">
+      <c r="A252" s="102" t="s">
         <v>407</v>
       </c>
-      <c r="B252" s="99"/>
-      <c r="C252" s="99"/>
-      <c r="D252" s="99"/>
-      <c r="E252" s="99"/>
+      <c r="B252" s="103"/>
+      <c r="C252" s="103"/>
+      <c r="D252" s="103"/>
+      <c r="E252" s="103"/>
     </row>
     <row r="253" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="6" t="s">
@@ -7824,13 +7842,13 @@
       </c>
     </row>
     <row r="258" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A258" s="101" t="s">
+      <c r="A258" s="102" t="s">
         <v>410</v>
       </c>
-      <c r="B258" s="99"/>
-      <c r="C258" s="99"/>
-      <c r="D258" s="99"/>
-      <c r="E258" s="99"/>
+      <c r="B258" s="103"/>
+      <c r="C258" s="103"/>
+      <c r="D258" s="103"/>
+      <c r="E258" s="103"/>
     </row>
     <row r="259" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="6" t="s">
@@ -7903,13 +7921,13 @@
       <c r="D264" s="12"/>
     </row>
     <row r="265" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="101" t="s">
+      <c r="A265" s="102" t="s">
         <v>450</v>
       </c>
-      <c r="B265" s="99"/>
-      <c r="C265" s="99"/>
-      <c r="D265" s="99"/>
-      <c r="E265" s="99"/>
+      <c r="B265" s="103"/>
+      <c r="C265" s="103"/>
+      <c r="D265" s="103"/>
+      <c r="E265" s="103"/>
     </row>
     <row r="266" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="6" t="s">
@@ -7980,13 +7998,13 @@
       </c>
     </row>
     <row r="270" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="101" t="s">
+      <c r="A270" s="102" t="s">
         <v>451</v>
       </c>
-      <c r="B270" s="99"/>
-      <c r="C270" s="99"/>
-      <c r="D270" s="99"/>
-      <c r="E270" s="99"/>
+      <c r="B270" s="103"/>
+      <c r="C270" s="103"/>
+      <c r="D270" s="103"/>
+      <c r="E270" s="103"/>
     </row>
     <row r="271" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="6" t="s">
@@ -8074,13 +8092,13 @@
       </c>
     </row>
     <row r="276" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="101" t="s">
+      <c r="A276" s="102" t="s">
         <v>452</v>
       </c>
-      <c r="B276" s="99"/>
-      <c r="C276" s="99"/>
-      <c r="D276" s="99"/>
-      <c r="E276" s="99"/>
+      <c r="B276" s="103"/>
+      <c r="C276" s="103"/>
+      <c r="D276" s="103"/>
+      <c r="E276" s="103"/>
     </row>
     <row r="277" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="6" t="s">
@@ -8153,13 +8171,13 @@
       <c r="D282" s="12"/>
     </row>
     <row r="283" spans="1:5" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="100" t="s">
+      <c r="A283" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="B283" s="100"/>
-      <c r="C283" s="100"/>
-      <c r="D283" s="100"/>
-      <c r="E283" s="100"/>
+      <c r="B283" s="112"/>
+      <c r="C283" s="112"/>
+      <c r="D283" s="112"/>
+      <c r="E283" s="112"/>
     </row>
     <row r="284" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
@@ -8298,13 +8316,13 @@
       </c>
     </row>
     <row r="292" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="106" t="s">
+      <c r="A292" s="107" t="s">
         <v>136</v>
       </c>
-      <c r="B292" s="107"/>
-      <c r="C292" s="107"/>
-      <c r="D292" s="107"/>
-      <c r="E292" s="108"/>
+      <c r="B292" s="108"/>
+      <c r="C292" s="108"/>
+      <c r="D292" s="108"/>
+      <c r="E292" s="109"/>
     </row>
     <row r="293" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A293" s="6" t="s">
@@ -8392,13 +8410,13 @@
       </c>
     </row>
     <row r="298" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A298" s="106" t="s">
+      <c r="A298" s="107" t="s">
         <v>148</v>
       </c>
-      <c r="B298" s="107"/>
-      <c r="C298" s="107"/>
-      <c r="D298" s="107"/>
-      <c r="E298" s="108"/>
+      <c r="B298" s="108"/>
+      <c r="C298" s="108"/>
+      <c r="D298" s="108"/>
+      <c r="E298" s="109"/>
     </row>
     <row r="299" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A299" s="6" t="s">
@@ -8469,13 +8487,13 @@
       </c>
     </row>
     <row r="303" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="102" t="s">
+      <c r="A303" s="104" t="s">
         <v>465</v>
       </c>
-      <c r="B303" s="103"/>
-      <c r="C303" s="103"/>
-      <c r="D303" s="103"/>
-      <c r="E303" s="104"/>
+      <c r="B303" s="105"/>
+      <c r="C303" s="105"/>
+      <c r="D303" s="105"/>
+      <c r="E303" s="106"/>
     </row>
     <row r="304" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A304" s="6" t="s">
@@ -8546,13 +8564,13 @@
       <c r="E310" s="17"/>
     </row>
     <row r="311" spans="1:5" s="41" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A311" s="101" t="s">
+      <c r="A311" s="102" t="s">
         <v>300</v>
       </c>
-      <c r="B311" s="99"/>
-      <c r="C311" s="99"/>
-      <c r="D311" s="99"/>
-      <c r="E311" s="99"/>
+      <c r="B311" s="103"/>
+      <c r="C311" s="103"/>
+      <c r="D311" s="103"/>
+      <c r="E311" s="103"/>
     </row>
     <row r="312" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A312" s="6" t="s">
@@ -8623,13 +8641,13 @@
       </c>
     </row>
     <row r="316" spans="1:5" s="41" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A316" s="101" t="s">
+      <c r="A316" s="102" t="s">
         <v>273</v>
       </c>
-      <c r="B316" s="99"/>
-      <c r="C316" s="99"/>
-      <c r="D316" s="99"/>
-      <c r="E316" s="99"/>
+      <c r="B316" s="103"/>
+      <c r="C316" s="103"/>
+      <c r="D316" s="103"/>
+      <c r="E316" s="103"/>
     </row>
     <row r="317" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A317" s="6" t="s">
@@ -8700,13 +8718,13 @@
       </c>
     </row>
     <row r="321" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A321" s="101" t="s">
+      <c r="A321" s="102" t="s">
         <v>438</v>
       </c>
-      <c r="B321" s="99"/>
-      <c r="C321" s="99"/>
-      <c r="D321" s="99"/>
-      <c r="E321" s="99"/>
+      <c r="B321" s="103"/>
+      <c r="C321" s="103"/>
+      <c r="D321" s="103"/>
+      <c r="E321" s="103"/>
     </row>
     <row r="322" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A322" s="6" t="s">
@@ -8794,13 +8812,13 @@
       </c>
     </row>
     <row r="327" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A327" s="101" t="s">
+      <c r="A327" s="102" t="s">
         <v>439</v>
       </c>
-      <c r="B327" s="99"/>
-      <c r="C327" s="99"/>
-      <c r="D327" s="99"/>
-      <c r="E327" s="99"/>
+      <c r="B327" s="103"/>
+      <c r="C327" s="103"/>
+      <c r="D327" s="103"/>
+      <c r="E327" s="103"/>
     </row>
     <row r="328" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A328" s="6" t="s">
@@ -8840,13 +8858,13 @@
       <c r="E330" s="17"/>
     </row>
     <row r="331" spans="1:5" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A331" s="101" t="s">
+      <c r="A331" s="102" t="s">
         <v>305</v>
       </c>
-      <c r="B331" s="99"/>
-      <c r="C331" s="99"/>
-      <c r="D331" s="99"/>
-      <c r="E331" s="99"/>
+      <c r="B331" s="103"/>
+      <c r="C331" s="103"/>
+      <c r="D331" s="103"/>
+      <c r="E331" s="103"/>
     </row>
     <row r="332" spans="1:5" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A332" s="6" t="s">
@@ -8917,13 +8935,13 @@
       </c>
     </row>
     <row r="336" spans="1:5" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A336" s="101" t="s">
+      <c r="A336" s="102" t="s">
         <v>290</v>
       </c>
-      <c r="B336" s="99"/>
-      <c r="C336" s="99"/>
-      <c r="D336" s="99"/>
-      <c r="E336" s="99"/>
+      <c r="B336" s="103"/>
+      <c r="C336" s="103"/>
+      <c r="D336" s="103"/>
+      <c r="E336" s="103"/>
     </row>
     <row r="337" spans="1:5" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A337" s="6" t="s">
@@ -9011,13 +9029,13 @@
       </c>
     </row>
     <row r="342" spans="1:5" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A342" s="106" t="s">
+      <c r="A342" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="B342" s="107"/>
-      <c r="C342" s="107"/>
-      <c r="D342" s="107"/>
-      <c r="E342" s="108"/>
+      <c r="B342" s="108"/>
+      <c r="C342" s="108"/>
+      <c r="D342" s="108"/>
+      <c r="E342" s="109"/>
     </row>
     <row r="343" spans="1:5" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A343" s="6" t="s">
@@ -9089,13 +9107,13 @@
       </c>
     </row>
     <row r="349" spans="1:5" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A349" s="101" t="s">
+      <c r="A349" s="102" t="s">
         <v>304</v>
       </c>
-      <c r="B349" s="99"/>
-      <c r="C349" s="99"/>
-      <c r="D349" s="99"/>
-      <c r="E349" s="99"/>
+      <c r="B349" s="103"/>
+      <c r="C349" s="103"/>
+      <c r="D349" s="103"/>
+      <c r="E349" s="103"/>
     </row>
     <row r="350" spans="1:5" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A350" s="6" t="s">
@@ -9183,13 +9201,13 @@
       </c>
     </row>
     <row r="355" spans="1:5" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A355" s="101" t="s">
+      <c r="A355" s="102" t="s">
         <v>306</v>
       </c>
-      <c r="B355" s="99"/>
-      <c r="C355" s="99"/>
-      <c r="D355" s="99"/>
-      <c r="E355" s="99"/>
+      <c r="B355" s="103"/>
+      <c r="C355" s="103"/>
+      <c r="D355" s="103"/>
+      <c r="E355" s="103"/>
     </row>
     <row r="356" spans="1:5" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A356" s="6" t="s">
@@ -9264,13 +9282,13 @@
       <c r="E361" s="17"/>
     </row>
     <row r="362" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A362" s="102" t="s">
+      <c r="A362" s="104" t="s">
         <v>450</v>
       </c>
-      <c r="B362" s="103"/>
-      <c r="C362" s="103"/>
-      <c r="D362" s="103"/>
-      <c r="E362" s="104"/>
+      <c r="B362" s="105"/>
+      <c r="C362" s="105"/>
+      <c r="D362" s="105"/>
+      <c r="E362" s="106"/>
     </row>
     <row r="363" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A363" s="6" t="s">
@@ -9341,13 +9359,13 @@
       </c>
     </row>
     <row r="367" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A367" s="101" t="s">
+      <c r="A367" s="102" t="s">
         <v>451</v>
       </c>
-      <c r="B367" s="99"/>
-      <c r="C367" s="99"/>
-      <c r="D367" s="99"/>
-      <c r="E367" s="99"/>
+      <c r="B367" s="103"/>
+      <c r="C367" s="103"/>
+      <c r="D367" s="103"/>
+      <c r="E367" s="103"/>
     </row>
     <row r="368" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A368" s="6" t="s">
@@ -9435,13 +9453,13 @@
       </c>
     </row>
     <row r="373" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A373" s="101" t="s">
+      <c r="A373" s="102" t="s">
         <v>452</v>
       </c>
-      <c r="B373" s="99"/>
-      <c r="C373" s="99"/>
-      <c r="D373" s="99"/>
-      <c r="E373" s="99"/>
+      <c r="B373" s="103"/>
+      <c r="C373" s="103"/>
+      <c r="D373" s="103"/>
+      <c r="E373" s="103"/>
     </row>
     <row r="374" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A374" s="6" t="s">
@@ -9514,13 +9532,13 @@
       <c r="D379" s="56"/>
     </row>
     <row r="380" spans="1:5" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A380" s="102" t="s">
+      <c r="A380" s="104" t="s">
         <v>422</v>
       </c>
-      <c r="B380" s="103"/>
-      <c r="C380" s="103"/>
-      <c r="D380" s="103"/>
-      <c r="E380" s="104"/>
+      <c r="B380" s="105"/>
+      <c r="C380" s="105"/>
+      <c r="D380" s="105"/>
+      <c r="E380" s="106"/>
     </row>
     <row r="381" spans="1:5" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A381" s="6" t="s">
@@ -9591,13 +9609,13 @@
       </c>
     </row>
     <row r="385" spans="1:8" s="42" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A385" s="101" t="s">
+      <c r="A385" s="102" t="s">
         <v>426</v>
       </c>
-      <c r="B385" s="99"/>
-      <c r="C385" s="99"/>
-      <c r="D385" s="99"/>
-      <c r="E385" s="99"/>
+      <c r="B385" s="103"/>
+      <c r="C385" s="103"/>
+      <c r="D385" s="103"/>
+      <c r="E385" s="103"/>
     </row>
     <row r="386" spans="1:8" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A386" s="6" t="s">
@@ -9685,13 +9703,13 @@
       </c>
     </row>
     <row r="391" spans="1:8" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A391" s="101" t="s">
+      <c r="A391" s="102" t="s">
         <v>427</v>
       </c>
-      <c r="B391" s="99"/>
-      <c r="C391" s="99"/>
-      <c r="D391" s="99"/>
-      <c r="E391" s="99"/>
+      <c r="B391" s="103"/>
+      <c r="C391" s="103"/>
+      <c r="D391" s="103"/>
+      <c r="E391" s="103"/>
     </row>
     <row r="392" spans="1:8" s="42" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A392" s="6" t="s">
@@ -9781,16 +9799,16 @@
       <c r="E399" s="17"/>
     </row>
     <row r="400" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A400" s="84" t="s">
+      <c r="A400" s="88" t="s">
         <v>191</v>
       </c>
-      <c r="B400" s="84"/>
-      <c r="C400" s="84"/>
-      <c r="D400" s="84"/>
-      <c r="E400" s="84"/>
-      <c r="F400" s="84"/>
-      <c r="G400" s="84"/>
-      <c r="H400" s="84"/>
+      <c r="B400" s="88"/>
+      <c r="C400" s="88"/>
+      <c r="D400" s="88"/>
+      <c r="E400" s="88"/>
+      <c r="F400" s="88"/>
+      <c r="G400" s="88"/>
+      <c r="H400" s="88"/>
     </row>
     <row r="401" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A401" s="2" t="s">
@@ -10116,13 +10134,13 @@
       </c>
     </row>
     <row r="420" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A420" s="99" t="s">
+      <c r="A420" s="103" t="s">
         <v>136</v>
       </c>
-      <c r="B420" s="99"/>
-      <c r="C420" s="99"/>
-      <c r="D420" s="99"/>
-      <c r="E420" s="99"/>
+      <c r="B420" s="103"/>
+      <c r="C420" s="103"/>
+      <c r="D420" s="103"/>
+      <c r="E420" s="103"/>
     </row>
     <row r="421" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A421" s="6" t="s">
@@ -10210,13 +10228,13 @@
       </c>
     </row>
     <row r="426" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A426" s="99" t="s">
+      <c r="A426" s="103" t="s">
         <v>148</v>
       </c>
-      <c r="B426" s="99"/>
-      <c r="C426" s="99"/>
-      <c r="D426" s="99"/>
-      <c r="E426" s="99"/>
+      <c r="B426" s="103"/>
+      <c r="C426" s="103"/>
+      <c r="D426" s="103"/>
+      <c r="E426" s="103"/>
     </row>
     <row r="427" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A427" s="6" t="s">
@@ -10287,13 +10305,13 @@
       </c>
     </row>
     <row r="431" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A431" s="99" t="s">
+      <c r="A431" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="B431" s="99"/>
-      <c r="C431" s="99"/>
-      <c r="D431" s="99"/>
-      <c r="E431" s="99"/>
+      <c r="B431" s="103"/>
+      <c r="C431" s="103"/>
+      <c r="D431" s="103"/>
+      <c r="E431" s="103"/>
     </row>
     <row r="432" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A432" s="6" t="s">
@@ -10367,13 +10385,13 @@
       </c>
     </row>
     <row r="438" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A438" s="100" t="s">
+      <c r="A438" s="112" t="s">
         <v>192</v>
       </c>
-      <c r="B438" s="100"/>
-      <c r="C438" s="100"/>
-      <c r="D438" s="100"/>
-      <c r="E438" s="100"/>
+      <c r="B438" s="112"/>
+      <c r="C438" s="112"/>
+      <c r="D438" s="112"/>
+      <c r="E438" s="112"/>
     </row>
     <row r="439" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A439" s="2" t="s">
@@ -10682,13 +10700,13 @@
       </c>
     </row>
     <row r="457" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A457" s="99" t="s">
+      <c r="A457" s="103" t="s">
         <v>136</v>
       </c>
-      <c r="B457" s="99"/>
-      <c r="C457" s="99"/>
-      <c r="D457" s="99"/>
-      <c r="E457" s="99"/>
+      <c r="B457" s="103"/>
+      <c r="C457" s="103"/>
+      <c r="D457" s="103"/>
+      <c r="E457" s="103"/>
     </row>
     <row r="458" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A458" s="6" t="s">
@@ -10776,13 +10794,13 @@
       </c>
     </row>
     <row r="463" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A463" s="99" t="s">
+      <c r="A463" s="103" t="s">
         <v>148</v>
       </c>
-      <c r="B463" s="99"/>
-      <c r="C463" s="99"/>
-      <c r="D463" s="99"/>
-      <c r="E463" s="99"/>
+      <c r="B463" s="103"/>
+      <c r="C463" s="103"/>
+      <c r="D463" s="103"/>
+      <c r="E463" s="103"/>
     </row>
     <row r="464" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A464" s="6" t="s">
@@ -10853,13 +10871,13 @@
       </c>
     </row>
     <row r="468" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A468" s="99" t="s">
+      <c r="A468" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="B468" s="99"/>
-      <c r="C468" s="99"/>
-      <c r="D468" s="99"/>
-      <c r="E468" s="99"/>
+      <c r="B468" s="103"/>
+      <c r="C468" s="103"/>
+      <c r="D468" s="103"/>
+      <c r="E468" s="103"/>
     </row>
     <row r="469" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A469" s="6" t="s">
@@ -10931,36 +10949,21 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="A270:E270"/>
-    <mergeCell ref="A276:E276"/>
-    <mergeCell ref="A362:E362"/>
-    <mergeCell ref="A367:E367"/>
-    <mergeCell ref="A373:E373"/>
-    <mergeCell ref="A292:E292"/>
-    <mergeCell ref="A298:E298"/>
-    <mergeCell ref="A303:E303"/>
-    <mergeCell ref="A331:E331"/>
-    <mergeCell ref="A336:E336"/>
-    <mergeCell ref="A342:E342"/>
-    <mergeCell ref="A349:E349"/>
-    <mergeCell ref="A355:E355"/>
-    <mergeCell ref="A187:E187"/>
-    <mergeCell ref="A169:E179"/>
-    <mergeCell ref="A182:E182"/>
-    <mergeCell ref="A190:E190"/>
-    <mergeCell ref="A265:E265"/>
-    <mergeCell ref="A252:E252"/>
-    <mergeCell ref="A258:E258"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A468:E468"/>
+    <mergeCell ref="A426:E426"/>
+    <mergeCell ref="A431:E431"/>
+    <mergeCell ref="A438:E438"/>
+    <mergeCell ref="A457:E457"/>
+    <mergeCell ref="A463:E463"/>
+    <mergeCell ref="A400:H400"/>
+    <mergeCell ref="A420:E420"/>
+    <mergeCell ref="A311:E311"/>
+    <mergeCell ref="A316:E316"/>
+    <mergeCell ref="A385:E385"/>
+    <mergeCell ref="A391:E391"/>
+    <mergeCell ref="A380:E380"/>
+    <mergeCell ref="A321:E321"/>
+    <mergeCell ref="A327:E327"/>
     <mergeCell ref="A103:E103"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="F110:K110"/>
@@ -10977,21 +10980,36 @@
     <mergeCell ref="A233:E233"/>
     <mergeCell ref="A239:E239"/>
     <mergeCell ref="A247:E247"/>
-    <mergeCell ref="A400:H400"/>
-    <mergeCell ref="A420:E420"/>
-    <mergeCell ref="A311:E311"/>
-    <mergeCell ref="A316:E316"/>
-    <mergeCell ref="A385:E385"/>
-    <mergeCell ref="A391:E391"/>
-    <mergeCell ref="A380:E380"/>
-    <mergeCell ref="A321:E321"/>
-    <mergeCell ref="A327:E327"/>
-    <mergeCell ref="A468:E468"/>
-    <mergeCell ref="A426:E426"/>
-    <mergeCell ref="A431:E431"/>
-    <mergeCell ref="A438:E438"/>
-    <mergeCell ref="A457:E457"/>
-    <mergeCell ref="A463:E463"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A187:E187"/>
+    <mergeCell ref="A169:E179"/>
+    <mergeCell ref="A182:E182"/>
+    <mergeCell ref="A190:E190"/>
+    <mergeCell ref="A265:E265"/>
+    <mergeCell ref="A252:E252"/>
+    <mergeCell ref="A258:E258"/>
+    <mergeCell ref="A270:E270"/>
+    <mergeCell ref="A276:E276"/>
+    <mergeCell ref="A362:E362"/>
+    <mergeCell ref="A367:E367"/>
+    <mergeCell ref="A373:E373"/>
+    <mergeCell ref="A292:E292"/>
+    <mergeCell ref="A298:E298"/>
+    <mergeCell ref="A303:E303"/>
+    <mergeCell ref="A331:E331"/>
+    <mergeCell ref="A336:E336"/>
+    <mergeCell ref="A342:E342"/>
+    <mergeCell ref="A349:E349"/>
+    <mergeCell ref="A355:E355"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11012,16 +11030,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="97" t="s">
         <v>494</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -11178,13 +11196,13 @@
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="99" t="s">
+      <c r="A9" s="103" t="s">
         <v>193</v>
       </c>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -11226,17 +11244,17 @@
       <c r="D11" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="E11" s="142" t="s">
+      <c r="E11" s="84" t="s">
         <v>334</v>
       </c>
-      <c r="F11" s="144" t="s">
+      <c r="F11" s="115" t="s">
         <v>240</v>
       </c>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="115"/>
       <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -11252,19 +11270,19 @@
       <c r="D12" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="E12" s="142" t="s">
+      <c r="E12" s="84" t="s">
         <v>337</v>
       </c>
-      <c r="F12" s="145" t="s">
+      <c r="F12" s="120" t="s">
         <v>628</v>
       </c>
-      <c r="G12" s="146"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="147" t="s">
+      <c r="G12" s="121"/>
+      <c r="H12" s="121"/>
+      <c r="I12" s="114" t="s">
         <v>633</v>
       </c>
-      <c r="J12" s="147"/>
-      <c r="K12" s="147"/>
+      <c r="J12" s="114"/>
+      <c r="K12" s="114"/>
       <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -11280,15 +11298,15 @@
       <c r="D13" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="E13" s="142" t="s">
+      <c r="E13" s="84" t="s">
         <v>340</v>
       </c>
-      <c r="F13" s="146"/>
-      <c r="G13" s="146"/>
-      <c r="H13" s="146"/>
-      <c r="I13" s="147"/>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="121"/>
+      <c r="H13" s="121"/>
+      <c r="I13" s="114"/>
+      <c r="J13" s="114"/>
+      <c r="K13" s="114"/>
       <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -11304,15 +11322,15 @@
       <c r="D14" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="E14" s="143" t="s">
+      <c r="E14" s="85" t="s">
         <v>343</v>
       </c>
-      <c r="F14" s="146"/>
-      <c r="G14" s="146"/>
-      <c r="H14" s="146"/>
-      <c r="I14" s="147"/>
-      <c r="J14" s="147"/>
-      <c r="K14" s="147"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="121"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="114"/>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -11328,15 +11346,15 @@
       <c r="D15" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="E15" s="142" t="s">
+      <c r="E15" s="84" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="146"/>
-      <c r="G15" s="146"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="147"/>
-      <c r="J15" s="147"/>
-      <c r="K15" s="147"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="121"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="114"/>
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -11352,15 +11370,15 @@
       <c r="D16" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="E16" s="142" t="s">
+      <c r="E16" s="84" t="s">
         <v>244</v>
       </c>
-      <c r="F16" s="146"/>
-      <c r="G16" s="146"/>
-      <c r="H16" s="146"/>
-      <c r="I16" s="147"/>
-      <c r="J16" s="147"/>
-      <c r="K16" s="147"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="121"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="114"/>
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -11376,15 +11394,15 @@
       <c r="D17" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="E17" s="142" t="s">
+      <c r="E17" s="84" t="s">
         <v>350</v>
       </c>
-      <c r="F17" s="146"/>
-      <c r="G17" s="146"/>
-      <c r="H17" s="146"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="147"/>
-      <c r="K17" s="147"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" s="79" customFormat="1" ht="33" x14ac:dyDescent="0.2">
@@ -11400,25 +11418,25 @@
       <c r="D18" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="E18" s="143" t="s">
+      <c r="E18" s="85" t="s">
         <v>622</v>
       </c>
-      <c r="F18" s="146"/>
-      <c r="G18" s="146"/>
-      <c r="H18" s="146"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="147"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="121"/>
+      <c r="I18" s="114"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114"/>
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="106" t="s">
+      <c r="A19" s="107" t="s">
         <v>629</v>
       </c>
-      <c r="B19" s="107"/>
-      <c r="C19" s="107"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="108"/>
+      <c r="B19" s="108"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="109"/>
     </row>
     <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
@@ -11489,13 +11507,13 @@
       </c>
     </row>
     <row r="24" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="106" t="s">
+      <c r="A24" s="107" t="s">
         <v>215</v>
       </c>
-      <c r="B24" s="107"/>
-      <c r="C24" s="107"/>
-      <c r="D24" s="107"/>
-      <c r="E24" s="108"/>
+      <c r="B24" s="108"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="108"/>
+      <c r="E24" s="109"/>
       <c r="F24" s="41"/>
       <c r="G24" s="41"/>
       <c r="H24" s="41"/>
@@ -11554,13 +11572,13 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="106" t="s">
+      <c r="A29" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="B29" s="107"/>
-      <c r="C29" s="107"/>
-      <c r="D29" s="107"/>
-      <c r="E29" s="108"/>
+      <c r="B29" s="108"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="109"/>
     </row>
     <row r="30" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
@@ -11631,16 +11649,16 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A36" s="111" t="s">
+      <c r="A36" s="116" t="s">
         <v>252</v>
       </c>
-      <c r="B36" s="112"/>
-      <c r="C36" s="112"/>
-      <c r="D36" s="112"/>
-      <c r="E36" s="112"/>
-      <c r="F36" s="112"/>
-      <c r="G36" s="112"/>
-      <c r="H36" s="113"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="118"/>
     </row>
     <row r="37" spans="1:8" ht="49.5" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
@@ -12008,13 +12026,13 @@
     </row>
     <row r="52" spans="1:8" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="53" spans="1:8" s="57" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="148" t="s">
+      <c r="A53" s="119" t="s">
         <v>495</v>
       </c>
-      <c r="B53" s="84"/>
-      <c r="C53" s="84"/>
-      <c r="D53" s="84"/>
-      <c r="E53" s="84"/>
+      <c r="B53" s="88"/>
+      <c r="C53" s="88"/>
+      <c r="D53" s="88"/>
+      <c r="E53" s="88"/>
     </row>
     <row r="54" spans="1:8" s="57" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A54" s="64" t="s">
@@ -12087,16 +12105,16 @@
     <row r="58" spans="1:8" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="59" spans="1:8" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="60" spans="1:8" s="57" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="87" t="s">
+      <c r="A60" s="97" t="s">
         <v>497</v>
       </c>
-      <c r="B60" s="84"/>
-      <c r="C60" s="84"/>
-      <c r="D60" s="84"/>
-      <c r="E60" s="84"/>
-      <c r="F60" s="87"/>
-      <c r="G60" s="84"/>
-      <c r="H60" s="84"/>
+      <c r="B60" s="88"/>
+      <c r="C60" s="88"/>
+      <c r="D60" s="88"/>
+      <c r="E60" s="88"/>
+      <c r="F60" s="97"/>
+      <c r="G60" s="88"/>
+      <c r="H60" s="88"/>
     </row>
     <row r="61" spans="1:8" s="57" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
@@ -12196,13 +12214,13 @@
       <c r="H65"/>
     </row>
     <row r="66" spans="1:8" s="57" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A66" s="102" t="s">
+      <c r="A66" s="104" t="s">
         <v>257</v>
       </c>
-      <c r="B66" s="107"/>
-      <c r="C66" s="107"/>
-      <c r="D66" s="107"/>
-      <c r="E66" s="108"/>
+      <c r="B66" s="108"/>
+      <c r="C66" s="108"/>
+      <c r="D66" s="108"/>
+      <c r="E66" s="109"/>
       <c r="F66"/>
       <c r="G66"/>
       <c r="H66"/>
@@ -12252,13 +12270,13 @@
     </row>
     <row r="70" spans="1:8" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="71" spans="1:8" s="57" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="87" t="s">
+      <c r="A71" s="97" t="s">
         <v>496</v>
       </c>
-      <c r="B71" s="84"/>
-      <c r="C71" s="84"/>
-      <c r="D71" s="84"/>
-      <c r="E71" s="84"/>
+      <c r="B71" s="88"/>
+      <c r="C71" s="88"/>
+      <c r="D71" s="88"/>
+      <c r="E71" s="88"/>
     </row>
     <row r="72" spans="1:8" s="57" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A72" s="64" t="s">
@@ -12330,6 +12348,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="F12:H18"/>
     <mergeCell ref="I12:K18"/>
     <mergeCell ref="F11:K11"/>
     <mergeCell ref="A71:E71"/>
@@ -12338,12 +12362,6 @@
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="F12:H18"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12367,22 +12385,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="134" t="s">
         <v>479</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
     </row>
     <row r="2" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="71" t="s">
@@ -12400,17 +12418,17 @@
       <c r="E2" s="72" t="s">
         <v>483</v>
       </c>
-      <c r="F2" s="134" t="s">
+      <c r="F2" s="125" t="s">
         <v>484</v>
       </c>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="128"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="127"/>
     </row>
     <row r="3" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" s="71"/>
@@ -12422,17 +12440,17 @@
         <v>218</v>
       </c>
       <c r="E3" s="72"/>
-      <c r="F3" s="134" t="s">
+      <c r="F3" s="125" t="s">
         <v>507</v>
       </c>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127"/>
-      <c r="N3" s="128"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="127"/>
     </row>
     <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="71"/>
@@ -12444,17 +12462,17 @@
         <v>218</v>
       </c>
       <c r="E4" s="72"/>
-      <c r="F4" s="134" t="s">
+      <c r="F4" s="125" t="s">
         <v>503</v>
       </c>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
-      <c r="N4" s="128"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="126"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+      <c r="N4" s="127"/>
     </row>
     <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="71"/>
@@ -12466,17 +12484,17 @@
         <v>218</v>
       </c>
       <c r="E5" s="72"/>
-      <c r="F5" s="134" t="s">
+      <c r="F5" s="125" t="s">
         <v>505</v>
       </c>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
-      <c r="L5" s="127"/>
-      <c r="M5" s="127"/>
-      <c r="N5" s="128"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="126"/>
+      <c r="M5" s="126"/>
+      <c r="N5" s="127"/>
     </row>
     <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="71"/>
@@ -12488,17 +12506,17 @@
         <v>218</v>
       </c>
       <c r="E6" s="72"/>
-      <c r="F6" s="134" t="s">
+      <c r="F6" s="125" t="s">
         <v>506</v>
       </c>
-      <c r="G6" s="127"/>
-      <c r="H6" s="127"/>
-      <c r="I6" s="127"/>
-      <c r="J6" s="127"/>
-      <c r="K6" s="127"/>
-      <c r="L6" s="127"/>
-      <c r="M6" s="127"/>
-      <c r="N6" s="128"/>
+      <c r="G6" s="126"/>
+      <c r="H6" s="126"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="126"/>
+      <c r="L6" s="126"/>
+      <c r="M6" s="126"/>
+      <c r="N6" s="127"/>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="71"/>
@@ -12510,17 +12528,17 @@
         <v>218</v>
       </c>
       <c r="E7" s="72"/>
-      <c r="F7" s="134" t="s">
+      <c r="F7" s="125" t="s">
         <v>509</v>
       </c>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="127"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="127"/>
-      <c r="M7" s="127"/>
-      <c r="N7" s="128"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="126"/>
+      <c r="M7" s="126"/>
+      <c r="N7" s="127"/>
     </row>
     <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="71"/>
@@ -12532,17 +12550,17 @@
         <v>218</v>
       </c>
       <c r="E8" s="72"/>
-      <c r="F8" s="134" t="s">
+      <c r="F8" s="125" t="s">
         <v>510</v>
       </c>
-      <c r="G8" s="127"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
-      <c r="J8" s="127"/>
-      <c r="K8" s="127"/>
-      <c r="L8" s="127"/>
-      <c r="M8" s="127"/>
-      <c r="N8" s="128"/>
+      <c r="G8" s="126"/>
+      <c r="H8" s="126"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="126"/>
+      <c r="K8" s="126"/>
+      <c r="L8" s="126"/>
+      <c r="M8" s="126"/>
+      <c r="N8" s="127"/>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="71"/>
@@ -12554,17 +12572,17 @@
         <v>218</v>
       </c>
       <c r="E9" s="72"/>
-      <c r="F9" s="134" t="s">
+      <c r="F9" s="125" t="s">
         <v>512</v>
       </c>
-      <c r="G9" s="127"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="127"/>
-      <c r="K9" s="127"/>
-      <c r="L9" s="127"/>
-      <c r="M9" s="127"/>
-      <c r="N9" s="128"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="126"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
+      <c r="M9" s="126"/>
+      <c r="N9" s="127"/>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="71"/>
@@ -12576,17 +12594,17 @@
         <v>513</v>
       </c>
       <c r="E10" s="72"/>
-      <c r="F10" s="134" t="s">
+      <c r="F10" s="125" t="s">
         <v>514</v>
       </c>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="127"/>
-      <c r="L10" s="127"/>
-      <c r="M10" s="127"/>
-      <c r="N10" s="128"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="126"/>
+      <c r="K10" s="126"/>
+      <c r="L10" s="126"/>
+      <c r="M10" s="126"/>
+      <c r="N10" s="127"/>
     </row>
     <row r="11" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="71"/>
@@ -12598,17 +12616,17 @@
         <v>218</v>
       </c>
       <c r="E11" s="72"/>
-      <c r="F11" s="134" t="s">
+      <c r="F11" s="125" t="s">
         <v>516</v>
       </c>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="127"/>
-      <c r="N11" s="128"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="126"/>
+      <c r="K11" s="126"/>
+      <c r="L11" s="126"/>
+      <c r="M11" s="126"/>
+      <c r="N11" s="127"/>
     </row>
     <row r="12" spans="1:14" ht="56.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="71"/>
@@ -12620,17 +12638,17 @@
         <v>517</v>
       </c>
       <c r="E12" s="72"/>
-      <c r="F12" s="135" t="s">
+      <c r="F12" s="131" t="s">
         <v>617</v>
       </c>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="130"/>
-      <c r="N12" s="131"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
+      <c r="L12" s="132"/>
+      <c r="M12" s="132"/>
+      <c r="N12" s="133"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="71"/>
@@ -12642,17 +12660,17 @@
         <v>551</v>
       </c>
       <c r="E13" s="72"/>
-      <c r="F13" s="134" t="s">
+      <c r="F13" s="125" t="s">
         <v>518</v>
       </c>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127"/>
-      <c r="K13" s="127"/>
-      <c r="L13" s="127"/>
-      <c r="M13" s="127"/>
-      <c r="N13" s="128"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="126"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="127"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="71"/>
@@ -12664,17 +12682,17 @@
         <v>519</v>
       </c>
       <c r="E14" s="72"/>
-      <c r="F14" s="134" t="s">
+      <c r="F14" s="125" t="s">
         <v>520</v>
       </c>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="127"/>
-      <c r="L14" s="127"/>
-      <c r="M14" s="127"/>
-      <c r="N14" s="128"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="126"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="126"/>
+      <c r="M14" s="126"/>
+      <c r="N14" s="127"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="71"/>
@@ -12686,17 +12704,17 @@
         <v>521</v>
       </c>
       <c r="E15" s="72"/>
-      <c r="F15" s="134" t="s">
+      <c r="F15" s="125" t="s">
         <v>522</v>
       </c>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="127"/>
-      <c r="K15" s="127"/>
-      <c r="L15" s="127"/>
-      <c r="M15" s="127"/>
-      <c r="N15" s="128"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="126"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="126"/>
+      <c r="M15" s="126"/>
+      <c r="N15" s="127"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="71"/>
@@ -12708,17 +12726,17 @@
         <v>524</v>
       </c>
       <c r="E16" s="72"/>
-      <c r="F16" s="134" t="s">
+      <c r="F16" s="125" t="s">
         <v>526</v>
       </c>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="127"/>
-      <c r="K16" s="127"/>
-      <c r="L16" s="127"/>
-      <c r="M16" s="127"/>
-      <c r="N16" s="128"/>
+      <c r="G16" s="126"/>
+      <c r="H16" s="126"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="126"/>
+      <c r="M16" s="126"/>
+      <c r="N16" s="127"/>
     </row>
     <row r="17" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="71"/>
@@ -12730,17 +12748,17 @@
         <v>523</v>
       </c>
       <c r="E17" s="72"/>
-      <c r="F17" s="134" t="s">
+      <c r="F17" s="125" t="s">
         <v>525</v>
       </c>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="127"/>
-      <c r="L17" s="127"/>
-      <c r="M17" s="127"/>
-      <c r="N17" s="128"/>
+      <c r="G17" s="126"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="127"/>
     </row>
     <row r="18" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="71"/>
@@ -12752,17 +12770,17 @@
         <v>527</v>
       </c>
       <c r="E18" s="72"/>
-      <c r="F18" s="134" t="s">
+      <c r="F18" s="125" t="s">
         <v>528</v>
       </c>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="127"/>
-      <c r="K18" s="127"/>
-      <c r="L18" s="127"/>
-      <c r="M18" s="127"/>
-      <c r="N18" s="128"/>
+      <c r="G18" s="126"/>
+      <c r="H18" s="126"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="126"/>
+      <c r="K18" s="126"/>
+      <c r="L18" s="126"/>
+      <c r="M18" s="126"/>
+      <c r="N18" s="127"/>
     </row>
     <row r="19" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="71"/>
@@ -12774,17 +12792,17 @@
         <v>529</v>
       </c>
       <c r="E19" s="72"/>
-      <c r="F19" s="134" t="s">
+      <c r="F19" s="125" t="s">
         <v>530</v>
       </c>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="127"/>
-      <c r="K19" s="127"/>
-      <c r="L19" s="127"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="128"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="127"/>
     </row>
     <row r="20" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="71"/>
@@ -12792,17 +12810,17 @@
       <c r="C20" s="71"/>
       <c r="D20" s="71"/>
       <c r="E20" s="72"/>
-      <c r="F20" s="134">
+      <c r="F20" s="125">
         <v>1</v>
       </c>
-      <c r="G20" s="127"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="127"/>
-      <c r="J20" s="127"/>
-      <c r="K20" s="127"/>
-      <c r="L20" s="127"/>
-      <c r="M20" s="127"/>
-      <c r="N20" s="128"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="126"/>
+      <c r="I20" s="126"/>
+      <c r="J20" s="126"/>
+      <c r="K20" s="126"/>
+      <c r="L20" s="126"/>
+      <c r="M20" s="126"/>
+      <c r="N20" s="127"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="62"/>
@@ -12810,51 +12828,51 @@
       <c r="C21" s="62"/>
       <c r="D21" s="62"/>
       <c r="E21" s="63"/>
-      <c r="F21" s="139"/>
-      <c r="G21" s="140"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="140"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="140"/>
-      <c r="N21" s="141"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="129"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="129"/>
+      <c r="K21" s="129"/>
+      <c r="L21" s="129"/>
+      <c r="M21" s="129"/>
+      <c r="N21" s="130"/>
     </row>
     <row r="22" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="136" t="s">
+      <c r="A22" s="122" t="s">
         <v>549</v>
       </c>
-      <c r="B22" s="137"/>
-      <c r="C22" s="137"/>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="137"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="137"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="137"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="138"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="123"/>
+      <c r="G22" s="123"/>
+      <c r="H22" s="123"/>
+      <c r="I22" s="123"/>
+      <c r="J22" s="123"/>
+      <c r="K22" s="123"/>
+      <c r="L22" s="123"/>
+      <c r="M22" s="123"/>
+      <c r="N22" s="124"/>
     </row>
     <row r="23" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="132" t="s">
+      <c r="A23" s="135" t="s">
         <v>533</v>
       </c>
-      <c r="B23" s="133"/>
-      <c r="C23" s="133"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="133"/>
-      <c r="J23" s="133"/>
-      <c r="K23" s="133"/>
-      <c r="L23" s="133"/>
-      <c r="M23" s="133"/>
-      <c r="N23" s="133"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="134"/>
+      <c r="D23" s="134"/>
+      <c r="E23" s="134"/>
+      <c r="F23" s="134"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="134"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="134"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="134"/>
+      <c r="N23" s="134"/>
     </row>
     <row r="24" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="71" t="s">
@@ -12872,17 +12890,17 @@
       <c r="E24" s="72" t="s">
         <v>483</v>
       </c>
-      <c r="F24" s="126" t="s">
+      <c r="F24" s="136" t="s">
         <v>534</v>
       </c>
-      <c r="G24" s="127"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="127"/>
-      <c r="J24" s="127"/>
-      <c r="K24" s="127"/>
-      <c r="L24" s="127"/>
-      <c r="M24" s="127"/>
-      <c r="N24" s="128"/>
+      <c r="G24" s="126"/>
+      <c r="H24" s="126"/>
+      <c r="I24" s="126"/>
+      <c r="J24" s="126"/>
+      <c r="K24" s="126"/>
+      <c r="L24" s="126"/>
+      <c r="M24" s="126"/>
+      <c r="N24" s="127"/>
     </row>
     <row r="25" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="71"/>
@@ -12894,17 +12912,17 @@
         <v>535</v>
       </c>
       <c r="E25" s="72"/>
-      <c r="F25" s="126" t="s">
+      <c r="F25" s="136" t="s">
         <v>536</v>
       </c>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="127"/>
-      <c r="K25" s="127"/>
-      <c r="L25" s="127"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="128"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="126"/>
+      <c r="K25" s="126"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="126"/>
+      <c r="N25" s="127"/>
     </row>
     <row r="26" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="71"/>
@@ -12916,17 +12934,17 @@
         <v>537</v>
       </c>
       <c r="E26" s="72"/>
-      <c r="F26" s="126" t="s">
+      <c r="F26" s="136" t="s">
         <v>538</v>
       </c>
-      <c r="G26" s="127"/>
-      <c r="H26" s="127"/>
-      <c r="I26" s="127"/>
-      <c r="J26" s="127"/>
-      <c r="K26" s="127"/>
-      <c r="L26" s="127"/>
-      <c r="M26" s="127"/>
-      <c r="N26" s="128"/>
+      <c r="G26" s="126"/>
+      <c r="H26" s="126"/>
+      <c r="I26" s="126"/>
+      <c r="J26" s="126"/>
+      <c r="K26" s="126"/>
+      <c r="L26" s="126"/>
+      <c r="M26" s="126"/>
+      <c r="N26" s="127"/>
     </row>
     <row r="27" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="71"/>
@@ -12938,17 +12956,17 @@
         <v>218</v>
       </c>
       <c r="E27" s="72"/>
-      <c r="F27" s="126" t="s">
+      <c r="F27" s="136" t="s">
         <v>540</v>
       </c>
-      <c r="G27" s="127"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="127"/>
-      <c r="J27" s="127"/>
-      <c r="K27" s="127"/>
-      <c r="L27" s="127"/>
-      <c r="M27" s="127"/>
-      <c r="N27" s="128"/>
+      <c r="G27" s="126"/>
+      <c r="H27" s="126"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="126"/>
+      <c r="K27" s="126"/>
+      <c r="L27" s="126"/>
+      <c r="M27" s="126"/>
+      <c r="N27" s="127"/>
     </row>
     <row r="28" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="71"/>
@@ -12960,17 +12978,17 @@
         <v>535</v>
       </c>
       <c r="E28" s="72"/>
-      <c r="F28" s="126" t="s">
+      <c r="F28" s="136" t="s">
         <v>539</v>
       </c>
-      <c r="G28" s="127"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="127"/>
-      <c r="J28" s="127"/>
-      <c r="K28" s="127"/>
-      <c r="L28" s="127"/>
-      <c r="M28" s="127"/>
-      <c r="N28" s="128"/>
+      <c r="G28" s="126"/>
+      <c r="H28" s="126"/>
+      <c r="I28" s="126"/>
+      <c r="J28" s="126"/>
+      <c r="K28" s="126"/>
+      <c r="L28" s="126"/>
+      <c r="M28" s="126"/>
+      <c r="N28" s="127"/>
     </row>
     <row r="29" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="71"/>
@@ -12982,17 +13000,17 @@
         <v>535</v>
       </c>
       <c r="E29" s="72"/>
-      <c r="F29" s="126" t="s">
+      <c r="F29" s="136" t="s">
         <v>541</v>
       </c>
-      <c r="G29" s="127"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="127"/>
-      <c r="J29" s="127"/>
-      <c r="K29" s="127"/>
-      <c r="L29" s="127"/>
-      <c r="M29" s="127"/>
-      <c r="N29" s="128"/>
+      <c r="G29" s="126"/>
+      <c r="H29" s="126"/>
+      <c r="I29" s="126"/>
+      <c r="J29" s="126"/>
+      <c r="K29" s="126"/>
+      <c r="L29" s="126"/>
+      <c r="M29" s="126"/>
+      <c r="N29" s="127"/>
     </row>
     <row r="30" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="71"/>
@@ -13004,17 +13022,17 @@
         <v>218</v>
       </c>
       <c r="E30" s="72"/>
-      <c r="F30" s="126" t="s">
+      <c r="F30" s="136" t="s">
         <v>543</v>
       </c>
-      <c r="G30" s="127"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="127"/>
-      <c r="J30" s="127"/>
-      <c r="K30" s="127"/>
-      <c r="L30" s="127"/>
-      <c r="M30" s="127"/>
-      <c r="N30" s="128"/>
+      <c r="G30" s="126"/>
+      <c r="H30" s="126"/>
+      <c r="I30" s="126"/>
+      <c r="J30" s="126"/>
+      <c r="K30" s="126"/>
+      <c r="L30" s="126"/>
+      <c r="M30" s="126"/>
+      <c r="N30" s="127"/>
     </row>
     <row r="31" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="71"/>
@@ -13026,17 +13044,17 @@
         <v>218</v>
       </c>
       <c r="E31" s="72"/>
-      <c r="F31" s="126" t="s">
+      <c r="F31" s="136" t="s">
         <v>545</v>
       </c>
-      <c r="G31" s="127"/>
-      <c r="H31" s="127"/>
-      <c r="I31" s="127"/>
-      <c r="J31" s="127"/>
-      <c r="K31" s="127"/>
-      <c r="L31" s="127"/>
-      <c r="M31" s="127"/>
-      <c r="N31" s="128"/>
+      <c r="G31" s="126"/>
+      <c r="H31" s="126"/>
+      <c r="I31" s="126"/>
+      <c r="J31" s="126"/>
+      <c r="K31" s="126"/>
+      <c r="L31" s="126"/>
+      <c r="M31" s="126"/>
+      <c r="N31" s="127"/>
     </row>
     <row r="32" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="71"/>
@@ -13048,17 +13066,17 @@
         <v>218</v>
       </c>
       <c r="E32" s="72"/>
-      <c r="F32" s="126" t="s">
+      <c r="F32" s="136" t="s">
         <v>546</v>
       </c>
-      <c r="G32" s="127"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="127"/>
-      <c r="J32" s="127"/>
-      <c r="K32" s="127"/>
-      <c r="L32" s="127"/>
-      <c r="M32" s="127"/>
-      <c r="N32" s="128"/>
+      <c r="G32" s="126"/>
+      <c r="H32" s="126"/>
+      <c r="I32" s="126"/>
+      <c r="J32" s="126"/>
+      <c r="K32" s="126"/>
+      <c r="L32" s="126"/>
+      <c r="M32" s="126"/>
+      <c r="N32" s="127"/>
     </row>
     <row r="33" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="71"/>
@@ -13070,17 +13088,17 @@
         <v>218</v>
       </c>
       <c r="E33" s="72"/>
-      <c r="F33" s="126" t="s">
+      <c r="F33" s="136" t="s">
         <v>547</v>
       </c>
-      <c r="G33" s="127"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="127"/>
-      <c r="J33" s="127"/>
-      <c r="K33" s="127"/>
-      <c r="L33" s="127"/>
-      <c r="M33" s="127"/>
-      <c r="N33" s="128"/>
+      <c r="G33" s="126"/>
+      <c r="H33" s="126"/>
+      <c r="I33" s="126"/>
+      <c r="J33" s="126"/>
+      <c r="K33" s="126"/>
+      <c r="L33" s="126"/>
+      <c r="M33" s="126"/>
+      <c r="N33" s="127"/>
     </row>
     <row r="34" spans="1:14" s="58" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A34" s="71"/>
@@ -13104,344 +13122,358 @@
       <c r="C35" s="71"/>
       <c r="D35" s="71"/>
       <c r="E35" s="72"/>
-      <c r="F35" s="129"/>
-      <c r="G35" s="130"/>
-      <c r="H35" s="130"/>
-      <c r="I35" s="130"/>
-      <c r="J35" s="130"/>
-      <c r="K35" s="130"/>
-      <c r="L35" s="130"/>
-      <c r="M35" s="130"/>
-      <c r="N35" s="131"/>
+      <c r="F35" s="149"/>
+      <c r="G35" s="132"/>
+      <c r="H35" s="132"/>
+      <c r="I35" s="132"/>
+      <c r="J35" s="132"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="132"/>
+      <c r="M35" s="132"/>
+      <c r="N35" s="133"/>
     </row>
     <row r="36" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="114" t="s">
+      <c r="A36" s="137" t="s">
         <v>548</v>
       </c>
-      <c r="B36" s="115"/>
-      <c r="C36" s="115"/>
-      <c r="D36" s="115"/>
-      <c r="E36" s="115"/>
-      <c r="F36" s="115"/>
-      <c r="G36" s="115"/>
-      <c r="H36" s="115"/>
-      <c r="I36" s="115"/>
-      <c r="J36" s="115"/>
-      <c r="K36" s="115"/>
-      <c r="L36" s="115"/>
-      <c r="M36" s="115"/>
-      <c r="N36" s="116"/>
+      <c r="B36" s="138"/>
+      <c r="C36" s="138"/>
+      <c r="D36" s="138"/>
+      <c r="E36" s="138"/>
+      <c r="F36" s="138"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
+      <c r="J36" s="138"/>
+      <c r="K36" s="138"/>
+      <c r="L36" s="138"/>
+      <c r="M36" s="138"/>
+      <c r="N36" s="139"/>
     </row>
     <row r="116" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="117" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D117" s="117" t="s">
+      <c r="D117" s="140" t="s">
         <v>550</v>
       </c>
-      <c r="E117" s="118"/>
-      <c r="F117" s="118"/>
-      <c r="G117" s="118"/>
-      <c r="H117" s="118"/>
-      <c r="I117" s="118"/>
-      <c r="J117" s="118"/>
-      <c r="K117" s="118"/>
-      <c r="L117" s="118"/>
-      <c r="M117" s="118"/>
-      <c r="N117" s="118"/>
-      <c r="O117" s="118"/>
-      <c r="P117" s="119"/>
+      <c r="E117" s="141"/>
+      <c r="F117" s="141"/>
+      <c r="G117" s="141"/>
+      <c r="H117" s="141"/>
+      <c r="I117" s="141"/>
+      <c r="J117" s="141"/>
+      <c r="K117" s="141"/>
+      <c r="L117" s="141"/>
+      <c r="M117" s="141"/>
+      <c r="N117" s="141"/>
+      <c r="O117" s="141"/>
+      <c r="P117" s="142"/>
     </row>
     <row r="118" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D118" s="120"/>
-      <c r="E118" s="121"/>
-      <c r="F118" s="121"/>
-      <c r="G118" s="121"/>
-      <c r="H118" s="121"/>
-      <c r="I118" s="121"/>
-      <c r="J118" s="121"/>
-      <c r="K118" s="121"/>
-      <c r="L118" s="121"/>
-      <c r="M118" s="121"/>
-      <c r="N118" s="121"/>
-      <c r="O118" s="121"/>
-      <c r="P118" s="122"/>
+      <c r="D118" s="143"/>
+      <c r="E118" s="144"/>
+      <c r="F118" s="144"/>
+      <c r="G118" s="144"/>
+      <c r="H118" s="144"/>
+      <c r="I118" s="144"/>
+      <c r="J118" s="144"/>
+      <c r="K118" s="144"/>
+      <c r="L118" s="144"/>
+      <c r="M118" s="144"/>
+      <c r="N118" s="144"/>
+      <c r="O118" s="144"/>
+      <c r="P118" s="145"/>
     </row>
     <row r="119" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D119" s="120"/>
-      <c r="E119" s="121"/>
-      <c r="F119" s="121"/>
-      <c r="G119" s="121"/>
-      <c r="H119" s="121"/>
-      <c r="I119" s="121"/>
-      <c r="J119" s="121"/>
-      <c r="K119" s="121"/>
-      <c r="L119" s="121"/>
-      <c r="M119" s="121"/>
-      <c r="N119" s="121"/>
-      <c r="O119" s="121"/>
-      <c r="P119" s="122"/>
+      <c r="D119" s="143"/>
+      <c r="E119" s="144"/>
+      <c r="F119" s="144"/>
+      <c r="G119" s="144"/>
+      <c r="H119" s="144"/>
+      <c r="I119" s="144"/>
+      <c r="J119" s="144"/>
+      <c r="K119" s="144"/>
+      <c r="L119" s="144"/>
+      <c r="M119" s="144"/>
+      <c r="N119" s="144"/>
+      <c r="O119" s="144"/>
+      <c r="P119" s="145"/>
     </row>
     <row r="120" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D120" s="120"/>
-      <c r="E120" s="121"/>
-      <c r="F120" s="121"/>
-      <c r="G120" s="121"/>
-      <c r="H120" s="121"/>
-      <c r="I120" s="121"/>
-      <c r="J120" s="121"/>
-      <c r="K120" s="121"/>
-      <c r="L120" s="121"/>
-      <c r="M120" s="121"/>
-      <c r="N120" s="121"/>
-      <c r="O120" s="121"/>
-      <c r="P120" s="122"/>
+      <c r="D120" s="143"/>
+      <c r="E120" s="144"/>
+      <c r="F120" s="144"/>
+      <c r="G120" s="144"/>
+      <c r="H120" s="144"/>
+      <c r="I120" s="144"/>
+      <c r="J120" s="144"/>
+      <c r="K120" s="144"/>
+      <c r="L120" s="144"/>
+      <c r="M120" s="144"/>
+      <c r="N120" s="144"/>
+      <c r="O120" s="144"/>
+      <c r="P120" s="145"/>
     </row>
     <row r="121" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D121" s="120"/>
-      <c r="E121" s="121"/>
-      <c r="F121" s="121"/>
-      <c r="G121" s="121"/>
-      <c r="H121" s="121"/>
-      <c r="I121" s="121"/>
-      <c r="J121" s="121"/>
-      <c r="K121" s="121"/>
-      <c r="L121" s="121"/>
-      <c r="M121" s="121"/>
-      <c r="N121" s="121"/>
-      <c r="O121" s="121"/>
-      <c r="P121" s="122"/>
+      <c r="D121" s="143"/>
+      <c r="E121" s="144"/>
+      <c r="F121" s="144"/>
+      <c r="G121" s="144"/>
+      <c r="H121" s="144"/>
+      <c r="I121" s="144"/>
+      <c r="J121" s="144"/>
+      <c r="K121" s="144"/>
+      <c r="L121" s="144"/>
+      <c r="M121" s="144"/>
+      <c r="N121" s="144"/>
+      <c r="O121" s="144"/>
+      <c r="P121" s="145"/>
     </row>
     <row r="122" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D122" s="120"/>
-      <c r="E122" s="121"/>
-      <c r="F122" s="121"/>
-      <c r="G122" s="121"/>
-      <c r="H122" s="121"/>
-      <c r="I122" s="121"/>
-      <c r="J122" s="121"/>
-      <c r="K122" s="121"/>
-      <c r="L122" s="121"/>
-      <c r="M122" s="121"/>
-      <c r="N122" s="121"/>
-      <c r="O122" s="121"/>
-      <c r="P122" s="122"/>
+      <c r="D122" s="143"/>
+      <c r="E122" s="144"/>
+      <c r="F122" s="144"/>
+      <c r="G122" s="144"/>
+      <c r="H122" s="144"/>
+      <c r="I122" s="144"/>
+      <c r="J122" s="144"/>
+      <c r="K122" s="144"/>
+      <c r="L122" s="144"/>
+      <c r="M122" s="144"/>
+      <c r="N122" s="144"/>
+      <c r="O122" s="144"/>
+      <c r="P122" s="145"/>
     </row>
     <row r="123" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D123" s="120"/>
-      <c r="E123" s="121"/>
-      <c r="F123" s="121"/>
-      <c r="G123" s="121"/>
-      <c r="H123" s="121"/>
-      <c r="I123" s="121"/>
-      <c r="J123" s="121"/>
-      <c r="K123" s="121"/>
-      <c r="L123" s="121"/>
-      <c r="M123" s="121"/>
-      <c r="N123" s="121"/>
-      <c r="O123" s="121"/>
-      <c r="P123" s="122"/>
+      <c r="D123" s="143"/>
+      <c r="E123" s="144"/>
+      <c r="F123" s="144"/>
+      <c r="G123" s="144"/>
+      <c r="H123" s="144"/>
+      <c r="I123" s="144"/>
+      <c r="J123" s="144"/>
+      <c r="K123" s="144"/>
+      <c r="L123" s="144"/>
+      <c r="M123" s="144"/>
+      <c r="N123" s="144"/>
+      <c r="O123" s="144"/>
+      <c r="P123" s="145"/>
     </row>
     <row r="124" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D124" s="120"/>
-      <c r="E124" s="121"/>
-      <c r="F124" s="121"/>
-      <c r="G124" s="121"/>
-      <c r="H124" s="121"/>
-      <c r="I124" s="121"/>
-      <c r="J124" s="121"/>
-      <c r="K124" s="121"/>
-      <c r="L124" s="121"/>
-      <c r="M124" s="121"/>
-      <c r="N124" s="121"/>
-      <c r="O124" s="121"/>
-      <c r="P124" s="122"/>
+      <c r="D124" s="143"/>
+      <c r="E124" s="144"/>
+      <c r="F124" s="144"/>
+      <c r="G124" s="144"/>
+      <c r="H124" s="144"/>
+      <c r="I124" s="144"/>
+      <c r="J124" s="144"/>
+      <c r="K124" s="144"/>
+      <c r="L124" s="144"/>
+      <c r="M124" s="144"/>
+      <c r="N124" s="144"/>
+      <c r="O124" s="144"/>
+      <c r="P124" s="145"/>
     </row>
     <row r="125" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D125" s="120"/>
-      <c r="E125" s="121"/>
-      <c r="F125" s="121"/>
-      <c r="G125" s="121"/>
-      <c r="H125" s="121"/>
-      <c r="I125" s="121"/>
-      <c r="J125" s="121"/>
-      <c r="K125" s="121"/>
-      <c r="L125" s="121"/>
-      <c r="M125" s="121"/>
-      <c r="N125" s="121"/>
-      <c r="O125" s="121"/>
-      <c r="P125" s="122"/>
+      <c r="D125" s="143"/>
+      <c r="E125" s="144"/>
+      <c r="F125" s="144"/>
+      <c r="G125" s="144"/>
+      <c r="H125" s="144"/>
+      <c r="I125" s="144"/>
+      <c r="J125" s="144"/>
+      <c r="K125" s="144"/>
+      <c r="L125" s="144"/>
+      <c r="M125" s="144"/>
+      <c r="N125" s="144"/>
+      <c r="O125" s="144"/>
+      <c r="P125" s="145"/>
     </row>
     <row r="126" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D126" s="120"/>
-      <c r="E126" s="121"/>
-      <c r="F126" s="121"/>
-      <c r="G126" s="121"/>
-      <c r="H126" s="121"/>
-      <c r="I126" s="121"/>
-      <c r="J126" s="121"/>
-      <c r="K126" s="121"/>
-      <c r="L126" s="121"/>
-      <c r="M126" s="121"/>
-      <c r="N126" s="121"/>
-      <c r="O126" s="121"/>
-      <c r="P126" s="122"/>
+      <c r="D126" s="143"/>
+      <c r="E126" s="144"/>
+      <c r="F126" s="144"/>
+      <c r="G126" s="144"/>
+      <c r="H126" s="144"/>
+      <c r="I126" s="144"/>
+      <c r="J126" s="144"/>
+      <c r="K126" s="144"/>
+      <c r="L126" s="144"/>
+      <c r="M126" s="144"/>
+      <c r="N126" s="144"/>
+      <c r="O126" s="144"/>
+      <c r="P126" s="145"/>
     </row>
     <row r="127" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D127" s="120"/>
-      <c r="E127" s="121"/>
-      <c r="F127" s="121"/>
-      <c r="G127" s="121"/>
-      <c r="H127" s="121"/>
-      <c r="I127" s="121"/>
-      <c r="J127" s="121"/>
-      <c r="K127" s="121"/>
-      <c r="L127" s="121"/>
-      <c r="M127" s="121"/>
-      <c r="N127" s="121"/>
-      <c r="O127" s="121"/>
-      <c r="P127" s="122"/>
+      <c r="D127" s="143"/>
+      <c r="E127" s="144"/>
+      <c r="F127" s="144"/>
+      <c r="G127" s="144"/>
+      <c r="H127" s="144"/>
+      <c r="I127" s="144"/>
+      <c r="J127" s="144"/>
+      <c r="K127" s="144"/>
+      <c r="L127" s="144"/>
+      <c r="M127" s="144"/>
+      <c r="N127" s="144"/>
+      <c r="O127" s="144"/>
+      <c r="P127" s="145"/>
     </row>
     <row r="128" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D128" s="120"/>
-      <c r="E128" s="121"/>
-      <c r="F128" s="121"/>
-      <c r="G128" s="121"/>
-      <c r="H128" s="121"/>
-      <c r="I128" s="121"/>
-      <c r="J128" s="121"/>
-      <c r="K128" s="121"/>
-      <c r="L128" s="121"/>
-      <c r="M128" s="121"/>
-      <c r="N128" s="121"/>
-      <c r="O128" s="121"/>
-      <c r="P128" s="122"/>
+      <c r="D128" s="143"/>
+      <c r="E128" s="144"/>
+      <c r="F128" s="144"/>
+      <c r="G128" s="144"/>
+      <c r="H128" s="144"/>
+      <c r="I128" s="144"/>
+      <c r="J128" s="144"/>
+      <c r="K128" s="144"/>
+      <c r="L128" s="144"/>
+      <c r="M128" s="144"/>
+      <c r="N128" s="144"/>
+      <c r="O128" s="144"/>
+      <c r="P128" s="145"/>
     </row>
     <row r="129" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D129" s="120"/>
-      <c r="E129" s="121"/>
-      <c r="F129" s="121"/>
-      <c r="G129" s="121"/>
-      <c r="H129" s="121"/>
-      <c r="I129" s="121"/>
-      <c r="J129" s="121"/>
-      <c r="K129" s="121"/>
-      <c r="L129" s="121"/>
-      <c r="M129" s="121"/>
-      <c r="N129" s="121"/>
-      <c r="O129" s="121"/>
-      <c r="P129" s="122"/>
+      <c r="D129" s="143"/>
+      <c r="E129" s="144"/>
+      <c r="F129" s="144"/>
+      <c r="G129" s="144"/>
+      <c r="H129" s="144"/>
+      <c r="I129" s="144"/>
+      <c r="J129" s="144"/>
+      <c r="K129" s="144"/>
+      <c r="L129" s="144"/>
+      <c r="M129" s="144"/>
+      <c r="N129" s="144"/>
+      <c r="O129" s="144"/>
+      <c r="P129" s="145"/>
     </row>
     <row r="130" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D130" s="120"/>
-      <c r="E130" s="121"/>
-      <c r="F130" s="121"/>
-      <c r="G130" s="121"/>
-      <c r="H130" s="121"/>
-      <c r="I130" s="121"/>
-      <c r="J130" s="121"/>
-      <c r="K130" s="121"/>
-      <c r="L130" s="121"/>
-      <c r="M130" s="121"/>
-      <c r="N130" s="121"/>
-      <c r="O130" s="121"/>
-      <c r="P130" s="122"/>
+      <c r="D130" s="143"/>
+      <c r="E130" s="144"/>
+      <c r="F130" s="144"/>
+      <c r="G130" s="144"/>
+      <c r="H130" s="144"/>
+      <c r="I130" s="144"/>
+      <c r="J130" s="144"/>
+      <c r="K130" s="144"/>
+      <c r="L130" s="144"/>
+      <c r="M130" s="144"/>
+      <c r="N130" s="144"/>
+      <c r="O130" s="144"/>
+      <c r="P130" s="145"/>
     </row>
     <row r="131" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D131" s="120"/>
-      <c r="E131" s="121"/>
-      <c r="F131" s="121"/>
-      <c r="G131" s="121"/>
-      <c r="H131" s="121"/>
-      <c r="I131" s="121"/>
-      <c r="J131" s="121"/>
-      <c r="K131" s="121"/>
-      <c r="L131" s="121"/>
-      <c r="M131" s="121"/>
-      <c r="N131" s="121"/>
-      <c r="O131" s="121"/>
-      <c r="P131" s="122"/>
+      <c r="D131" s="143"/>
+      <c r="E131" s="144"/>
+      <c r="F131" s="144"/>
+      <c r="G131" s="144"/>
+      <c r="H131" s="144"/>
+      <c r="I131" s="144"/>
+      <c r="J131" s="144"/>
+      <c r="K131" s="144"/>
+      <c r="L131" s="144"/>
+      <c r="M131" s="144"/>
+      <c r="N131" s="144"/>
+      <c r="O131" s="144"/>
+      <c r="P131" s="145"/>
     </row>
     <row r="132" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D132" s="120"/>
-      <c r="E132" s="121"/>
-      <c r="F132" s="121"/>
-      <c r="G132" s="121"/>
-      <c r="H132" s="121"/>
-      <c r="I132" s="121"/>
-      <c r="J132" s="121"/>
-      <c r="K132" s="121"/>
-      <c r="L132" s="121"/>
-      <c r="M132" s="121"/>
-      <c r="N132" s="121"/>
-      <c r="O132" s="121"/>
-      <c r="P132" s="122"/>
+      <c r="D132" s="143"/>
+      <c r="E132" s="144"/>
+      <c r="F132" s="144"/>
+      <c r="G132" s="144"/>
+      <c r="H132" s="144"/>
+      <c r="I132" s="144"/>
+      <c r="J132" s="144"/>
+      <c r="K132" s="144"/>
+      <c r="L132" s="144"/>
+      <c r="M132" s="144"/>
+      <c r="N132" s="144"/>
+      <c r="O132" s="144"/>
+      <c r="P132" s="145"/>
     </row>
     <row r="133" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D133" s="120"/>
-      <c r="E133" s="121"/>
-      <c r="F133" s="121"/>
-      <c r="G133" s="121"/>
-      <c r="H133" s="121"/>
-      <c r="I133" s="121"/>
-      <c r="J133" s="121"/>
-      <c r="K133" s="121"/>
-      <c r="L133" s="121"/>
-      <c r="M133" s="121"/>
-      <c r="N133" s="121"/>
-      <c r="O133" s="121"/>
-      <c r="P133" s="122"/>
+      <c r="D133" s="143"/>
+      <c r="E133" s="144"/>
+      <c r="F133" s="144"/>
+      <c r="G133" s="144"/>
+      <c r="H133" s="144"/>
+      <c r="I133" s="144"/>
+      <c r="J133" s="144"/>
+      <c r="K133" s="144"/>
+      <c r="L133" s="144"/>
+      <c r="M133" s="144"/>
+      <c r="N133" s="144"/>
+      <c r="O133" s="144"/>
+      <c r="P133" s="145"/>
     </row>
     <row r="134" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D134" s="120"/>
-      <c r="E134" s="121"/>
-      <c r="F134" s="121"/>
-      <c r="G134" s="121"/>
-      <c r="H134" s="121"/>
-      <c r="I134" s="121"/>
-      <c r="J134" s="121"/>
-      <c r="K134" s="121"/>
-      <c r="L134" s="121"/>
-      <c r="M134" s="121"/>
-      <c r="N134" s="121"/>
-      <c r="O134" s="121"/>
-      <c r="P134" s="122"/>
+      <c r="D134" s="143"/>
+      <c r="E134" s="144"/>
+      <c r="F134" s="144"/>
+      <c r="G134" s="144"/>
+      <c r="H134" s="144"/>
+      <c r="I134" s="144"/>
+      <c r="J134" s="144"/>
+      <c r="K134" s="144"/>
+      <c r="L134" s="144"/>
+      <c r="M134" s="144"/>
+      <c r="N134" s="144"/>
+      <c r="O134" s="144"/>
+      <c r="P134" s="145"/>
     </row>
     <row r="135" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D135" s="120"/>
-      <c r="E135" s="121"/>
-      <c r="F135" s="121"/>
-      <c r="G135" s="121"/>
-      <c r="H135" s="121"/>
-      <c r="I135" s="121"/>
-      <c r="J135" s="121"/>
-      <c r="K135" s="121"/>
-      <c r="L135" s="121"/>
-      <c r="M135" s="121"/>
-      <c r="N135" s="121"/>
-      <c r="O135" s="121"/>
-      <c r="P135" s="122"/>
+      <c r="D135" s="143"/>
+      <c r="E135" s="144"/>
+      <c r="F135" s="144"/>
+      <c r="G135" s="144"/>
+      <c r="H135" s="144"/>
+      <c r="I135" s="144"/>
+      <c r="J135" s="144"/>
+      <c r="K135" s="144"/>
+      <c r="L135" s="144"/>
+      <c r="M135" s="144"/>
+      <c r="N135" s="144"/>
+      <c r="O135" s="144"/>
+      <c r="P135" s="145"/>
     </row>
     <row r="136" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D136" s="123"/>
-      <c r="E136" s="124"/>
-      <c r="F136" s="124"/>
-      <c r="G136" s="124"/>
-      <c r="H136" s="124"/>
-      <c r="I136" s="124"/>
-      <c r="J136" s="124"/>
-      <c r="K136" s="124"/>
-      <c r="L136" s="124"/>
-      <c r="M136" s="124"/>
-      <c r="N136" s="124"/>
-      <c r="O136" s="124"/>
-      <c r="P136" s="125"/>
+      <c r="D136" s="146"/>
+      <c r="E136" s="147"/>
+      <c r="F136" s="147"/>
+      <c r="G136" s="147"/>
+      <c r="H136" s="147"/>
+      <c r="I136" s="147"/>
+      <c r="J136" s="147"/>
+      <c r="K136" s="147"/>
+      <c r="L136" s="147"/>
+      <c r="M136" s="147"/>
+      <c r="N136" s="147"/>
+      <c r="O136" s="147"/>
+      <c r="P136" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="F18:N18"/>
-    <mergeCell ref="F19:N19"/>
-    <mergeCell ref="F20:N20"/>
-    <mergeCell ref="F21:N21"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="D117:P136"/>
+    <mergeCell ref="F33:N33"/>
+    <mergeCell ref="F35:N35"/>
+    <mergeCell ref="F28:N28"/>
+    <mergeCell ref="F29:N29"/>
+    <mergeCell ref="F30:N30"/>
+    <mergeCell ref="F31:N31"/>
+    <mergeCell ref="F32:N32"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="F24:N24"/>
+    <mergeCell ref="F25:N25"/>
+    <mergeCell ref="F26:N26"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="F2:N2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F3:N3"/>
+    <mergeCell ref="F4:N4"/>
+    <mergeCell ref="F5:N5"/>
     <mergeCell ref="F17:N17"/>
     <mergeCell ref="F6:N6"/>
     <mergeCell ref="F7:N7"/>
@@ -13454,25 +13486,11 @@
     <mergeCell ref="F14:N14"/>
     <mergeCell ref="F15:N15"/>
     <mergeCell ref="F16:N16"/>
-    <mergeCell ref="F2:N2"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="F3:N3"/>
-    <mergeCell ref="F4:N4"/>
-    <mergeCell ref="F5:N5"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="F24:N24"/>
-    <mergeCell ref="F25:N25"/>
-    <mergeCell ref="F26:N26"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="A36:N36"/>
-    <mergeCell ref="D117:P136"/>
-    <mergeCell ref="F33:N33"/>
-    <mergeCell ref="F35:N35"/>
-    <mergeCell ref="F28:N28"/>
-    <mergeCell ref="F29:N29"/>
-    <mergeCell ref="F30:N30"/>
-    <mergeCell ref="F31:N31"/>
-    <mergeCell ref="F32:N32"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="F18:N18"/>
+    <mergeCell ref="F19:N19"/>
+    <mergeCell ref="F20:N20"/>
+    <mergeCell ref="F21:N21"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
